--- a/results/Supplementary_Tables_S1-S6.xlsx
+++ b/results/Supplementary_Tables_S1-S6.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">S4_NIST — NIST SP 800-22 results (100 bitstreams of 10^6 bits per sequence): for every test (and every template, excursion state, or variant), the number of passing bitstreams and the P-value of the uniformity test. Sequences: three of the GPU filler function (three seeds) and one of the system generator of each of configurations B (OpenSSL) and C (Windows, BCryptGenRandom).</t>
   </si>
   <si>
-    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the revision kit (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean as reported by BenchmarkDotNet; N = measured iterations after the removal of upper outliers, pooled over the processes; Process 1-3 = mean of the iterations of each process, computed from the BenchmarkDotNet log.</t>
+    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the revision kit (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean (Student t, N - 1 degrees of freedom); N = measured iterations after the removal of upper outliers, pooled over the processes. Mean, CI, SD and SE are computed from the times of these iterations in the BenchmarkDotNet logs, as BenchmarkDotNet computes them; they agree with its reports, which round them to three or four significant digits, and the manuscript uses them. Median, quartiles, extremes, allocation and collections are those of the reports. Process 1-3 = mean of the measured iterations of each process after the removal of upper outliers (WorkloadResult lines of the log).</t>
   </si>
   <si>
     <t xml:space="preserve">   Source: results/configuration_D of the repository (CSV reports and logs); analysis/config_d.py recomputes the tables of the manuscript and checks the means and N of the logs against the reports.</t>
@@ -694,7 +694,7 @@
     <t xml:space="preserve">LinearComplexity</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S5. BenchmarkDotNet statistics of configuration D (all cases of the revision kit). Times in ms. CV = SD / Mean (formula). Process means from the BenchmarkDotNet logs; empty for the classes run in one process.</t>
+    <t xml:space="preserve">Table S5. BenchmarkDotNet statistics of configuration D (all cases of the revision kit). Times in ms. Mean, CI, SD and SE computed from the iteration times of the BenchmarkDotNet logs (see README); CV = SD / Mean (formula). Process means from the logs; Process 2 and 3 empty for the classes run in one process.</t>
   </si>
   <si>
     <t xml:space="preserve">Class</t>
@@ -935,14 +935,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="0.000000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000###"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1046,7 +1047,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1092,6 +1093,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1391,7 +1396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -29917,17 +29922,17 @@
       <c r="H4" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="I4" s="6" t="n">
-        <v>0.8416</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>0.02322</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>0.06199</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>0.0068</v>
+      <c r="I4" s="11" t="n">
+        <v>0.84159156626506</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>0.023222801951841</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0.0619863639702201</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0.00680388737064282</v>
       </c>
       <c r="M4" s="6" t="n">
         <v>0.8314</v>
@@ -29944,9 +29949,9 @@
       <c r="Q4" s="6" t="n">
         <v>1.0336</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="12" t="n">
         <f aca="false">K4/I4*100</f>
-        <v>7.3657319391635</v>
+        <v>7.36537371035126</v>
       </c>
       <c r="S4" s="5" t="n">
         <v>2</v>
@@ -29960,13 +29965,13 @@
       <c r="V4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="11" t="n">
         <v>0.84732962962963</v>
       </c>
-      <c r="X4" s="6" t="n">
+      <c r="X4" s="11" t="n">
         <v>0.827733333333333</v>
       </c>
-      <c r="Y4" s="6" t="n">
+      <c r="Y4" s="11" t="n">
         <v>0.849151724137931</v>
       </c>
     </row>
@@ -29995,17 +30000,17 @@
       <c r="H5" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <v>3.9289</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>0.05127</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0.14121</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0.01505</v>
+      <c r="I5" s="11" t="n">
+        <v>3.92891818181818</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0.0512687002837055</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>0.1412089000691</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>0.01505291932526</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>3.9292</v>
@@ -30022,9 +30027,9 @@
       <c r="Q5" s="6" t="n">
         <v>4.2082</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="12" t="n">
         <f aca="false">K5/I5*100</f>
-        <v>3.59413576319072</v>
+        <v>3.59409113487197</v>
       </c>
       <c r="S5" s="5" t="n">
         <v>33.07</v>
@@ -30038,13 +30043,13 @@
       <c r="V5" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" s="11" t="n">
         <v>4.01633666666667</v>
       </c>
-      <c r="X5" s="6" t="n">
+      <c r="X5" s="11" t="n">
         <v>3.89382857142857</v>
       </c>
-      <c r="Y5" s="6" t="n">
+      <c r="Y5" s="11" t="n">
         <v>3.87425</v>
       </c>
     </row>
@@ -30073,17 +30078,17 @@
       <c r="H6" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>4.1478</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>0.19602</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>0.53661</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>0.05753</v>
+      <c r="I6" s="11" t="n">
+        <v>4.14781379310345</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0.196024222822242</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.536613185393138</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0.0575309722419221</v>
       </c>
       <c r="M6" s="6" t="n">
         <v>3.9202</v>
@@ -30100,9 +30105,9 @@
       <c r="Q6" s="6" t="n">
         <v>5.5744</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="12" t="n">
         <f aca="false">K6/I6*100</f>
-        <v>12.9372197309417</v>
+        <v>12.9372535065427</v>
       </c>
       <c r="S6" s="5" t="n">
         <v>33.07</v>
@@ -30116,13 +30121,13 @@
       <c r="V6" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W6" s="6" t="n">
+      <c r="W6" s="11" t="n">
         <v>4.85614482758621</v>
       </c>
-      <c r="X6" s="6" t="n">
+      <c r="X6" s="11" t="n">
         <v>3.84840333333333</v>
       </c>
-      <c r="Y6" s="6" t="n">
+      <c r="Y6" s="11" t="n">
         <v>3.73498214285714</v>
       </c>
     </row>
@@ -30151,17 +30156,17 @@
       <c r="H7" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="I7" s="6" t="n">
-        <v>3.1514</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>0.05786</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>0.16032</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0.01699</v>
+      <c r="I7" s="11" t="n">
+        <v>3.15142359550562</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.0578581193333284</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.160324587678242</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0.016994372305183</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>3.1638</v>
@@ -30178,9 +30183,9 @@
       <c r="Q7" s="6" t="n">
         <v>3.52</v>
       </c>
-      <c r="R7" s="11" t="n">
+      <c r="R7" s="12" t="n">
         <f aca="false">K7/I7*100</f>
-        <v>5.08726280383322</v>
+        <v>5.08737028899851</v>
       </c>
       <c r="S7" s="5" t="n">
         <v>2.01</v>
@@ -30194,13 +30199,13 @@
       <c r="V7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="6" t="n">
+      <c r="W7" s="11" t="n">
         <v>3.12967586206897</v>
       </c>
-      <c r="X7" s="6" t="n">
+      <c r="X7" s="11" t="n">
         <v>3.19761666666667</v>
       </c>
-      <c r="Y7" s="6" t="n">
+      <c r="Y7" s="11" t="n">
         <v>3.12625333333333</v>
       </c>
     </row>
@@ -30229,17 +30234,17 @@
       <c r="H8" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I8" s="6" t="n">
-        <v>3.9376</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0.05039</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0.13709</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0.01478</v>
+      <c r="I8" s="11" t="n">
+        <v>3.93757558139535</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.0503893916291177</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0.137088066100974</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0.0147825863407643</v>
       </c>
       <c r="M8" s="6" t="n">
         <v>3.9391</v>
@@ -30256,9 +30261,9 @@
       <c r="Q8" s="6" t="n">
         <v>4.2584</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="12" t="n">
         <f aca="false">K8/I8*100</f>
-        <v>3.4815623730191</v>
+        <v>3.48153484973601</v>
       </c>
       <c r="S8" s="5" t="n">
         <v>33.63</v>
@@ -30272,13 +30277,13 @@
       <c r="V8" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W8" s="6" t="n">
+      <c r="W8" s="11" t="n">
         <v>3.92441666666667</v>
       </c>
-      <c r="X8" s="6" t="n">
+      <c r="X8" s="11" t="n">
         <v>3.9553275862069</v>
       </c>
-      <c r="Y8" s="6" t="n">
+      <c r="Y8" s="11" t="n">
         <v>3.93312962962963</v>
       </c>
     </row>
@@ -30307,17 +30312,17 @@
       <c r="H9" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>4.1402</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0.05745</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0.15631</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0.01686</v>
+      <c r="I9" s="11" t="n">
+        <v>4.14022674418605</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0.0574539115046914</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0.156307614826676</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>0.0168550835795753</v>
       </c>
       <c r="M9" s="6" t="n">
         <v>4.1129</v>
@@ -30334,9 +30339,9 @@
       <c r="Q9" s="6" t="n">
         <v>4.6037</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="12" t="n">
         <f aca="false">K9/I9*100</f>
-        <v>3.77542147722332</v>
+        <v>3.77533947980439</v>
       </c>
       <c r="S9" s="5" t="n">
         <v>33.63</v>
@@ -30350,13 +30355,13 @@
       <c r="V9" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W9" s="6" t="n">
+      <c r="W9" s="11" t="n">
         <v>4.12753103448276</v>
       </c>
-      <c r="X9" s="6" t="n">
+      <c r="X9" s="11" t="n">
         <v>4.12053214285714</v>
       </c>
-      <c r="Y9" s="6" t="n">
+      <c r="Y9" s="11" t="n">
         <v>4.17193793103448</v>
       </c>
     </row>
@@ -30385,17 +30390,17 @@
       <c r="H10" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>5.6638</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0.11733</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>0.32316</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0.03445</v>
+      <c r="I10" s="11" t="n">
+        <v>5.66382272727273</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0.117329567077798</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0.323159725543215</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>0.034448942491548</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>5.6955</v>
@@ -30412,9 +30417,9 @@
       <c r="Q10" s="6" t="n">
         <v>6.2796</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" s="12" t="n">
         <f aca="false">K10/I10*100</f>
-        <v>5.70570994738515</v>
+        <v>5.7056822062442</v>
       </c>
       <c r="S10" s="5" t="n">
         <v>2.02</v>
@@ -30428,13 +30433,13 @@
       <c r="V10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="6" t="n">
+      <c r="W10" s="11" t="n">
         <v>5.66614137931035</v>
       </c>
-      <c r="X10" s="6" t="n">
+      <c r="X10" s="11" t="n">
         <v>5.60632413793103</v>
       </c>
-      <c r="Y10" s="6" t="n">
+      <c r="Y10" s="11" t="n">
         <v>5.71716333333333</v>
       </c>
     </row>
@@ -30463,17 +30468,17 @@
       <c r="H11" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>5.1707</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0.05655</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>0.15575</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0.0166</v>
+      <c r="I11" s="11" t="n">
+        <v>5.1707125</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.0565471616173099</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.155747316585433</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>0.0166027197332392</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>5.1438</v>
@@ -30490,9 +30495,9 @@
       <c r="Q11" s="6" t="n">
         <v>5.5336</v>
       </c>
-      <c r="R11" s="11" t="n">
+      <c r="R11" s="12" t="n">
         <f aca="false">K11/I11*100</f>
-        <v>3.01216469723635</v>
+        <v>3.01210551902535</v>
       </c>
       <c r="S11" s="5" t="n">
         <v>34.24</v>
@@ -30506,13 +30511,13 @@
       <c r="V11" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="11" t="n">
         <v>5.17811379310345</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="11" t="n">
         <v>5.15681034482759</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="11" t="n">
         <v>5.17699666666667</v>
       </c>
     </row>
@@ -30541,17 +30546,17 @@
       <c r="H12" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="I12" s="6" t="n">
-        <v>5.7434</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.05328</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0.14585</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0.01564</v>
+      <c r="I12" s="11" t="n">
+        <v>5.74341379310345</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.0532775607261707</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0.14584647325536</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>0.0156363832138957</v>
       </c>
       <c r="M12" s="6" t="n">
         <v>5.7292</v>
@@ -30568,9 +30573,9 @@
       <c r="Q12" s="6" t="n">
         <v>6.0755</v>
       </c>
-      <c r="R12" s="11" t="n">
+      <c r="R12" s="12" t="n">
         <f aca="false">K12/I12*100</f>
-        <v>2.53943657067242</v>
+        <v>2.53936906706059</v>
       </c>
       <c r="S12" s="5" t="n">
         <v>34.24</v>
@@ -30584,13 +30589,13 @@
       <c r="V12" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="11" t="n">
         <v>5.71698965517241</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="11" t="n">
         <v>5.75876</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="11" t="n">
         <v>5.75433928571429</v>
       </c>
     </row>
@@ -30619,17 +30624,17 @@
       <c r="H13" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>8.3385</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0.15293</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0.42376</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0.04492</v>
+      <c r="I13" s="11" t="n">
+        <v>8.3385202247191</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.152925526935322</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0.423755945300148</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>0.0449180403658248</v>
       </c>
       <c r="M13" s="6" t="n">
         <v>8.3383</v>
@@ -30646,9 +30651,9 @@
       <c r="Q13" s="6" t="n">
         <v>9.3195</v>
       </c>
-      <c r="R13" s="11" t="n">
+      <c r="R13" s="12" t="n">
         <f aca="false">K13/I13*100</f>
-        <v>5.08196917910895</v>
+        <v>5.08190822688114</v>
       </c>
       <c r="S13" s="5" t="n">
         <v>2.03</v>
@@ -30662,13 +30667,13 @@
       <c r="V13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="W13" s="11" t="n">
         <v>8.34748</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="11" t="n">
         <v>8.32788275862069</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="11" t="n">
         <v>8.33984333333333</v>
       </c>
     </row>
@@ -30697,17 +30702,17 @@
       <c r="H14" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>5.5951</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>0.06405</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0.17535</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>0.0188</v>
+      <c r="I14" s="11" t="n">
+        <v>5.59514942528736</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0.0640539696443509</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>0.175346720895304</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>0.018799141741456</v>
       </c>
       <c r="M14" s="6" t="n">
         <v>5.5998</v>
@@ -30724,9 +30729,9 @@
       <c r="Q14" s="6" t="n">
         <v>5.9846</v>
       </c>
-      <c r="R14" s="11" t="n">
+      <c r="R14" s="12" t="n">
         <f aca="false">K14/I14*100</f>
-        <v>3.13399224321281</v>
+        <v>3.13390595258854</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>34.86</v>
@@ -30740,13 +30745,13 @@
       <c r="V14" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="11" t="n">
         <v>5.67466333333333</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="11" t="n">
         <v>5.53261724137931</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="11" t="n">
         <v>5.57472142857143</v>
       </c>
     </row>
@@ -30775,17 +30780,17 @@
       <c r="H15" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>6.3925</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.05869</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0.15966</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0.01722</v>
+      <c r="I15" s="11" t="n">
+        <v>6.39245813953488</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0.0586851856522726</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0.159657387194924</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>0.0172162988236437</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>6.3958</v>
@@ -30802,9 +30807,9 @@
       <c r="Q15" s="6" t="n">
         <v>6.9028</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="12" t="n">
         <f aca="false">K15/I15*100</f>
-        <v>2.49761439186547</v>
+        <v>2.49758987403459</v>
       </c>
       <c r="S15" s="5" t="n">
         <v>34.86</v>
@@ -30818,13 +30823,13 @@
       <c r="V15" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="11" t="n">
         <v>6.3758</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="11" t="n">
         <v>6.37704827586207</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="11" t="n">
         <v>6.42567142857143</v>
       </c>
     </row>
@@ -30853,17 +30858,17 @@
       <c r="H16" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>10.9407</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0.19805</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>0.5455</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0.05815</v>
+      <c r="I16" s="11" t="n">
+        <v>10.9407306818182</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.198053566082879</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0.54549707846241</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0.0581501839490392</v>
       </c>
       <c r="M16" s="6" t="n">
         <v>10.9294</v>
@@ -30880,9 +30885,9 @@
       <c r="Q16" s="6" t="n">
         <v>12.2603</v>
       </c>
-      <c r="R16" s="11" t="n">
+      <c r="R16" s="12" t="n">
         <f aca="false">K16/I16*100</f>
-        <v>4.98596981911578</v>
+        <v>4.98592913331595</v>
       </c>
       <c r="S16" s="5" t="n">
         <v>2.04</v>
@@ -30896,13 +30901,13 @@
       <c r="V16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="11" t="n">
         <v>11.0838566666667</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="11" t="n">
         <v>10.8320206896552</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="11" t="n">
         <v>10.9013793103448</v>
       </c>
     </row>
@@ -30931,17 +30936,17 @@
       <c r="H17" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I17" s="6" t="n">
-        <v>4.5978</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0.06357</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0.1751</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0.01867</v>
+      <c r="I17" s="11" t="n">
+        <v>4.59781363636364</v>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>0.0635730496589595</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>0.17509865408531</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>0.0186655792419456</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>4.57</v>
@@ -30958,9 +30963,9 @@
       <c r="Q17" s="6" t="n">
         <v>5.0879</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="12" t="n">
         <f aca="false">K17/I17*100</f>
-        <v>3.80834312062291</v>
+        <v>3.80830255277144</v>
       </c>
       <c r="S17" s="5" t="n">
         <v>33.47</v>
@@ -30974,13 +30979,13 @@
       <c r="V17" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="11" t="n">
         <v>4.66942</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="11" t="n">
         <v>4.56065862068965</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="11" t="n">
         <v>4.56089310344828</v>
       </c>
     </row>
@@ -31009,17 +31014,17 @@
       <c r="H18" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="I18" s="6" t="n">
-        <v>5.6077</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0.05564</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0.15417</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>0.01634</v>
+      <c r="I18" s="11" t="n">
+        <v>5.60765842696629</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0.0556367475241045</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>0.154169176415353</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>0.0163419000162601</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>5.6015</v>
@@ -31036,9 +31041,9 @@
       <c r="Q18" s="6" t="n">
         <v>5.9545</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <f aca="false">K18/I18*100</f>
-        <v>2.74925548798973</v>
+        <v>2.74926118313447</v>
       </c>
       <c r="S18" s="5" t="n">
         <v>33.47</v>
@@ -31052,13 +31057,13 @@
       <c r="V18" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="11" t="n">
         <v>5.5988724137931</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="11" t="n">
         <v>5.62149666666667</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="11" t="n">
         <v>5.60231333333333</v>
       </c>
     </row>
@@ -31087,17 +31092,17 @@
       <c r="H19" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>13.2808</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0.2175</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0.59173</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0.06381</v>
+      <c r="I19" s="11" t="n">
+        <v>13.2808395348837</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.217501165176198</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>0.591728003548345</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>0.0638076716047521</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>13.2344</v>
@@ -31114,9 +31119,9 @@
       <c r="Q19" s="6" t="n">
         <v>14.6799</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="12" t="n">
         <f aca="false">K19/I19*100</f>
-        <v>4.45552978736221</v>
+        <v>4.45550149140874</v>
       </c>
       <c r="S19" s="5" t="n">
         <v>2.05</v>
@@ -31130,13 +31135,13 @@
       <c r="V19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" s="11" t="n">
         <v>13.1352857142857</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="11" t="n">
         <v>13.5071206896552</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="11" t="n">
         <v>13.1950931034483</v>
       </c>
     </row>
@@ -31165,17 +31170,17 @@
       <c r="H20" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="I20" s="6" t="n">
-        <v>4.7129</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0.04268</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0.11538</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>0.01251</v>
+      <c r="I20" s="11" t="n">
+        <v>4.71288588235294</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>0.0426765507282531</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>0.115378544833271</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>0.0125145602765659</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>4.6985</v>
@@ -31192,9 +31197,9 @@
       <c r="Q20" s="6" t="n">
         <v>5.0213</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <f aca="false">K20/I20*100</f>
-        <v>2.44817416028348</v>
+        <v>2.44815061755044</v>
       </c>
       <c r="S20" s="5" t="n">
         <v>34.09</v>
@@ -31208,13 +31213,13 @@
       <c r="V20" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="W20" s="11" t="n">
         <v>4.70394827586207</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="11" t="n">
         <v>4.7240724137931</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="11" t="n">
         <v>4.71047037037037</v>
       </c>
     </row>
@@ -31243,17 +31248,17 @@
       <c r="H21" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>6.1289</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.06325</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0.17422</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0.01857</v>
+      <c r="I21" s="11" t="n">
+        <v>6.12889772727273</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>0.0632535108927995</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>0.174218551460332</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>0.0185717599868898</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>6.1279</v>
@@ -31270,9 +31275,9 @@
       <c r="Q21" s="6" t="n">
         <v>6.5694</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="12" t="n">
         <f aca="false">K21/I21*100</f>
-        <v>2.84259818238183</v>
+        <v>2.84257560189141</v>
       </c>
       <c r="S21" s="5" t="n">
         <v>34.09</v>
@@ -31286,13 +31291,13 @@
       <c r="V21" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="11" t="n">
         <v>6.1386275862069</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="11" t="n">
         <v>6.06946551724138</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="11" t="n">
         <v>6.17694333333333</v>
       </c>
     </row>
@@ -31321,17 +31326,17 @@
       <c r="H22" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>15.9913</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0.87808</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0.09256</v>
+      <c r="I22" s="11" t="n">
+        <v>15.9912988888889</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>0.314995647070076</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>0.878082023182888</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0.0925579721902233</v>
       </c>
       <c r="M22" s="6" t="n">
         <v>16.042</v>
@@ -31348,9 +31353,9 @@
       <c r="Q22" s="6" t="n">
         <v>17.9007</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <f aca="false">K22/I22*100</f>
-        <v>5.49098572348715</v>
+        <v>5.49099875678641</v>
       </c>
       <c r="S22" s="5" t="n">
         <v>2.06</v>
@@ -31364,13 +31369,13 @@
       <c r="V22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="11" t="n">
         <v>16.0970233333333</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="11" t="n">
         <v>16.2589366666667</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="11" t="n">
         <v>15.6179366666667</v>
       </c>
     </row>
@@ -31399,17 +31404,17 @@
       <c r="H23" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>6.0818</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0.05951</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0.16291</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0.01747</v>
+      <c r="I23" s="11" t="n">
+        <v>6.08175057471264</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0.0595122249637951</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0.162913767226688</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>0.0174661891941379</v>
       </c>
       <c r="M23" s="6" t="n">
         <v>6.094</v>
@@ -31426,9 +31431,9 @@
       <c r="Q23" s="6" t="n">
         <v>6.6106</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="12" t="n">
         <f aca="false">K23/I23*100</f>
-        <v>2.67864776875267</v>
+        <v>2.67873148076918</v>
       </c>
       <c r="S23" s="5" t="n">
         <v>34.7</v>
@@ -31442,13 +31447,13 @@
       <c r="V23" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="11" t="n">
         <v>6.07441034482759</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="11" t="n">
         <v>6.072475</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="11" t="n">
         <v>6.09750333333333</v>
       </c>
     </row>
@@ -31477,17 +31482,17 @@
       <c r="H24" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <v>7.7511</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.08182</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0.2226</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0.024</v>
+      <c r="I24" s="11" t="n">
+        <v>7.75112790697674</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>0.0818226153885969</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>0.22260447574971</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>0.0240040579475887</v>
       </c>
       <c r="M24" s="6" t="n">
         <v>7.7179</v>
@@ -31504,9 +31509,9 @@
       <c r="Q24" s="6" t="n">
         <v>8.3417</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="12" t="n">
         <f aca="false">K24/I24*100</f>
-        <v>2.87185044703332</v>
+        <v>2.87189785049663</v>
       </c>
       <c r="S24" s="5" t="n">
         <v>34.7</v>
@@ -31520,13 +31525,13 @@
       <c r="V24" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="11" t="n">
         <v>7.71210333333333</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="11" t="n">
         <v>7.71874827586207</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="11" t="n">
         <v>7.82926666666667</v>
       </c>
     </row>
@@ -31555,17 +31560,17 @@
       <c r="H25" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>20.136</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>0.4262</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>1.181</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0.12519</v>
+      <c r="I25" s="11" t="n">
+        <v>20.1360168539326</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>0.426200576854149</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>1.1809998758983</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>0.125185736473998</v>
       </c>
       <c r="M25" s="6" t="n">
         <v>20.2332</v>
@@ -31582,9 +31587,9 @@
       <c r="Q25" s="6" t="n">
         <v>22.5106</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R25" s="12" t="n">
         <f aca="false">K25/I25*100</f>
-        <v>5.86511720301947</v>
+        <v>5.86511167757418</v>
       </c>
       <c r="S25" s="5" t="n">
         <v>2.07</v>
@@ -31598,13 +31603,13 @@
       <c r="V25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="11" t="n">
         <v>20.6632965517241</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="11" t="n">
         <v>19.57363</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="11" t="n">
         <v>20.1887</v>
       </c>
     </row>
@@ -31633,17 +31638,17 @@
       <c r="H26" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="I26" s="6" t="n">
-        <v>7.5164</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>0.06893</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0.18987</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>0.02024</v>
+      <c r="I26" s="11" t="n">
+        <v>7.51637045454546</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.068934492540588</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.18986562590064</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>0.0202397437266613</v>
       </c>
       <c r="M26" s="6" t="n">
         <v>7.5129</v>
@@ -31660,9 +31665,9 @@
       <c r="Q26" s="6" t="n">
         <v>7.9487</v>
       </c>
-      <c r="R26" s="11" t="n">
+      <c r="R26" s="12" t="n">
         <f aca="false">K26/I26*100</f>
-        <v>2.52607631312863</v>
+        <v>2.52602804836236</v>
       </c>
       <c r="S26" s="5" t="n">
         <v>35.62</v>
@@ -31676,13 +31681,13 @@
       <c r="V26" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="11" t="n">
         <v>7.54497931034483</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="11" t="n">
         <v>7.47764137931034</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="11" t="n">
         <v>7.52615333333333</v>
       </c>
     </row>
@@ -31711,17 +31716,17 @@
       <c r="H27" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I27" s="6" t="n">
-        <v>8.7878</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.10246</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.27874</v>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0.03006</v>
+      <c r="I27" s="11" t="n">
+        <v>8.78777790697674</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.102455391961151</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.278737470159399</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>0.0300570344029987</v>
       </c>
       <c r="M27" s="6" t="n">
         <v>8.7249</v>
@@ -31738,9 +31743,9 @@
       <c r="Q27" s="6" t="n">
         <v>9.5219</v>
       </c>
-      <c r="R27" s="11" t="n">
+      <c r="R27" s="12" t="n">
         <f aca="false">K27/I27*100</f>
-        <v>3.1718974032181</v>
+        <v>3.17187658939475</v>
       </c>
       <c r="S27" s="5" t="n">
         <v>35.63</v>
@@ -31754,13 +31759,13 @@
       <c r="V27" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="11" t="n">
         <v>8.69247931034483</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="11" t="n">
         <v>8.79434642857143</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="11" t="n">
         <v>8.87673448275862</v>
       </c>
     </row>
@@ -31789,17 +31794,17 @@
       <c r="H28" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0.52024</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>1.45023</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0.15287</v>
+      <c r="I28" s="11" t="n">
+        <v>26.1100333333333</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.520242493148692</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>1.45022823387806</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>0.152867478204601</v>
       </c>
       <c r="M28" s="6" t="n">
         <v>26.2172</v>
@@ -31816,9 +31821,9 @@
       <c r="Q28" s="6" t="n">
         <v>29.1573</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="12" t="n">
         <f aca="false">K28/I28*100</f>
-        <v>5.55430869398698</v>
+        <v>5.55429483893699</v>
       </c>
       <c r="S28" s="5" t="n">
         <v>2.1</v>
@@ -31832,13 +31837,13 @@
       <c r="V28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="11" t="n">
         <v>26.2140066666667</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="11" t="n">
         <v>26.38493</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="11" t="n">
         <v>25.7311633333333</v>
       </c>
     </row>
@@ -31867,17 +31872,17 @@
       <c r="H29" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>8.8328</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.07306</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>0.20001</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>0.02144</v>
+      <c r="I29" s="11" t="n">
+        <v>8.83282988505747</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.0730640545147357</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.200011684609223</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>0.0214435034183571</v>
       </c>
       <c r="M29" s="6" t="n">
         <v>8.7969</v>
@@ -31894,9 +31899,9 @@
       <c r="Q29" s="6" t="n">
         <v>9.2276</v>
       </c>
-      <c r="R29" s="11" t="n">
+      <c r="R29" s="12" t="n">
         <f aca="false">K29/I29*100</f>
-        <v>2.26440086948646</v>
+        <v>2.26441228023176</v>
       </c>
       <c r="S29" s="5" t="n">
         <v>37.16</v>
@@ -31910,13 +31915,13 @@
       <c r="V29" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="11" t="n">
         <v>8.89497333333333</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="11" t="n">
         <v>8.77372413793103</v>
       </c>
-      <c r="Y29" s="6" t="n">
+      <c r="Y29" s="11" t="n">
         <v>8.82746428571429</v>
       </c>
     </row>
@@ -31945,17 +31950,17 @@
       <c r="H30" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="I30" s="6" t="n">
-        <v>11.0096</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>0.15403</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0.41905</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0.04519</v>
+      <c r="I30" s="11" t="n">
+        <v>11.0096337209302</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>0.154028892584722</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>0.419046992341787</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>0.0451869992867749</v>
       </c>
       <c r="M30" s="6" t="n">
         <v>10.911</v>
@@ -31972,9 +31977,9 @@
       <c r="Q30" s="6" t="n">
         <v>12.2023</v>
       </c>
-      <c r="R30" s="11" t="n">
+      <c r="R30" s="12" t="n">
         <f aca="false">K30/I30*100</f>
-        <v>3.80622365935184</v>
+        <v>3.80618468301215</v>
       </c>
       <c r="S30" s="5" t="n">
         <v>37.16</v>
@@ -31988,13 +31993,13 @@
       <c r="V30" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="W30" s="6" t="n">
+      <c r="W30" s="11" t="n">
         <v>10.7281192307692</v>
       </c>
-      <c r="X30" s="6" t="n">
+      <c r="X30" s="11" t="n">
         <v>11.2405333333333</v>
       </c>
-      <c r="Y30" s="6" t="n">
+      <c r="Y30" s="11" t="n">
         <v>11.0227133333333</v>
       </c>
     </row>
@@ -32023,17 +32028,17 @@
       <c r="H31" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>2879</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>177.4</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>35.2</v>
+      <c r="I31" s="11" t="n">
+        <v>2878.64346666667</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>177.361661797317</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>105.545080024225</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>35.1816933414082</v>
       </c>
       <c r="M31" s="6" t="n">
         <v>2868</v>
@@ -32050,9 +32055,9 @@
       <c r="Q31" s="6" t="n">
         <v>2995</v>
       </c>
-      <c r="R31" s="11" t="n">
+      <c r="R31" s="12" t="n">
         <f aca="false">K31/I31*100</f>
-        <v>3.66446682875999</v>
+        <v>3.66648670619988</v>
       </c>
       <c r="S31" s="5" t="n">
         <v>133.6</v>
@@ -32060,7 +32065,7 @@
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
       <c r="V31" s="5"/>
-      <c r="W31" s="6" t="n">
+      <c r="W31" s="11" t="n">
         <v>2878.64346666667</v>
       </c>
       <c r="X31" s="5"/>
@@ -32091,17 +32096,17 @@
       <c r="H32" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I32" s="6" t="n">
-        <v>3072</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>174.6</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>36.5</v>
+      <c r="I32" s="11" t="n">
+        <v>3072.36297</v>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>174.589628137322</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>115.480229105304</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>36.5180548690828</v>
       </c>
       <c r="M32" s="6" t="n">
         <v>3044</v>
@@ -32118,9 +32123,9 @@
       <c r="Q32" s="6" t="n">
         <v>3259</v>
       </c>
-      <c r="R32" s="11" t="n">
+      <c r="R32" s="12" t="n">
         <f aca="false">K32/I32*100</f>
-        <v>3.759765625</v>
+        <v>3.75867793723941</v>
       </c>
       <c r="S32" s="5" t="n">
         <v>133.58</v>
@@ -32128,7 +32133,7 @@
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
-      <c r="W32" s="6" t="n">
+      <c r="W32" s="11" t="n">
         <v>3072.36297</v>
       </c>
       <c r="X32" s="5"/>
@@ -32159,17 +32164,17 @@
       <c r="H33" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <v>2493</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>75.6</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="L33" s="6" t="n">
-        <v>15</v>
+      <c r="I33" s="11" t="n">
+        <v>2493.2531</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>75.5987215395863</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>44.9875865717978</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>14.9958621905993</v>
       </c>
       <c r="M33" s="6" t="n">
         <v>2473</v>
@@ -32186,9 +32191,9 @@
       <c r="Q33" s="6" t="n">
         <v>2591</v>
       </c>
-      <c r="R33" s="11" t="n">
+      <c r="R33" s="12" t="n">
         <f aca="false">K33/I33*100</f>
-        <v>1.80505415162455</v>
+        <v>1.80437303263747</v>
       </c>
       <c r="S33" s="5" t="n">
         <v>132.92</v>
@@ -32196,7 +32201,7 @@
       <c r="T33" s="5"/>
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
-      <c r="W33" s="6" t="n">
+      <c r="W33" s="11" t="n">
         <v>2493.2531</v>
       </c>
       <c r="X33" s="5"/>
@@ -32227,17 +32232,17 @@
       <c r="H34" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I34" s="6" t="n">
-        <v>2689</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>230.9</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>137.4</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>45.8</v>
+      <c r="I34" s="11" t="n">
+        <v>2689.09060555556</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>230.93575026173</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>137.426160731865</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>45.8087202439549</v>
       </c>
       <c r="M34" s="6" t="n">
         <v>2641</v>
@@ -32254,9 +32259,9 @@
       <c r="Q34" s="6" t="n">
         <v>2943</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="R34" s="12" t="n">
         <f aca="false">K34/I34*100</f>
-        <v>5.10970621048717</v>
+        <v>5.110506892105</v>
       </c>
       <c r="S34" s="5" t="n">
         <v>131.25</v>
@@ -32264,7 +32269,7 @@
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
-      <c r="W34" s="6" t="n">
+      <c r="W34" s="11" t="n">
         <v>2689.09060555556</v>
       </c>
       <c r="X34" s="5"/>
@@ -32295,17 +32300,17 @@
       <c r="H35" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I35" s="6" t="n">
-        <v>2686</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>169</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>33.5</v>
+      <c r="I35" s="11" t="n">
+        <v>2686.17267777778</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>169.045412637878</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>100.5962135435</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>33.5320711811667</v>
       </c>
       <c r="M35" s="6" t="n">
         <v>2652</v>
@@ -32322,9 +32327,9 @@
       <c r="Q35" s="6" t="n">
         <v>2849</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="12" t="n">
         <f aca="false">K35/I35*100</f>
-        <v>3.74534623976173</v>
+        <v>3.744964513105</v>
       </c>
       <c r="S35" s="5" t="n">
         <v>131.25</v>
@@ -32332,7 +32337,7 @@
       <c r="T35" s="5"/>
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
-      <c r="W35" s="6" t="n">
+      <c r="W35" s="11" t="n">
         <v>2686.17267777778</v>
       </c>
       <c r="X35" s="5"/>
@@ -32363,17 +32368,17 @@
       <c r="H36" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I36" s="6" t="n">
-        <v>5656</v>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>182.4</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="L36" s="6" t="n">
-        <v>36.2</v>
+      <c r="I36" s="11" t="n">
+        <v>5656.14545555556</v>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>182.414293587866</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>108.551820157703</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>36.1839400525677</v>
       </c>
       <c r="M36" s="6" t="n">
         <v>5645</v>
@@ -32390,9 +32395,9 @@
       <c r="Q36" s="6" t="n">
         <v>5829</v>
       </c>
-      <c r="R36" s="11" t="n">
+      <c r="R36" s="12" t="n">
         <f aca="false">K36/I36*100</f>
-        <v>1.92008486562942</v>
+        <v>1.91918367394675</v>
       </c>
       <c r="S36" s="5" t="n">
         <v>131.33</v>
@@ -32400,7 +32405,7 @@
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
-      <c r="W36" s="6" t="n">
+      <c r="W36" s="11" t="n">
         <v>5656.14545555556</v>
       </c>
       <c r="X36" s="5"/>
@@ -32431,17 +32436,17 @@
       <c r="H37" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>3896</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="L37" s="6" t="n">
-        <v>37.3</v>
+      <c r="I37" s="11" t="n">
+        <v>3896.40336</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>178.156523042012</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>117.839509236562</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>37.2641247543986</v>
       </c>
       <c r="M37" s="6" t="n">
         <v>3902</v>
@@ -32458,9 +32463,9 @@
       <c r="Q37" s="6" t="n">
         <v>4102</v>
       </c>
-      <c r="R37" s="11" t="n">
+      <c r="R37" s="12" t="n">
         <f aca="false">K37/I37*100</f>
-        <v>3.02361396303901</v>
+        <v>3.02431494763319</v>
       </c>
       <c r="S37" s="5" t="n">
         <v>131.33</v>
@@ -32468,7 +32473,7 @@
       <c r="T37" s="5"/>
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
-      <c r="W37" s="6" t="n">
+      <c r="W37" s="11" t="n">
         <v>3896.40336</v>
       </c>
       <c r="X37" s="5"/>
@@ -32499,17 +32504,17 @@
       <c r="H38" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I38" s="6" t="n">
-        <v>24797</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>1418.9</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>938.5</v>
-      </c>
-      <c r="L38" s="6" t="n">
-        <v>296.8</v>
+      <c r="I38" s="11" t="n">
+        <v>24796.53952</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>1418.92085495525</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>938.528291518242</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>296.788704970413</v>
       </c>
       <c r="M38" s="6" t="n">
         <v>24844</v>
@@ -32526,9 +32531,9 @@
       <c r="Q38" s="6" t="n">
         <v>26022</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="12" t="n">
         <f aca="false">K38/I38*100</f>
-        <v>3.78473202403517</v>
+        <v>3.78491640239259</v>
       </c>
       <c r="S38" s="5" t="n">
         <v>102</v>
@@ -32536,7 +32541,7 @@
       <c r="T38" s="5"/>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
-      <c r="W38" s="6" t="n">
+      <c r="W38" s="11" t="n">
         <v>24796.53952</v>
       </c>
       <c r="X38" s="5"/>
@@ -32567,17 +32572,17 @@
       <c r="H39" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I39" s="6" t="n">
-        <v>2668</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="L39" s="6" t="n">
-        <v>34.9</v>
+      <c r="I39" s="11" t="n">
+        <v>2668.45426666667</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>176.029115172611</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>104.752102902138</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>34.9173676340458</v>
       </c>
       <c r="M39" s="6" t="n">
         <v>2646</v>
@@ -32594,9 +32599,9 @@
       <c r="Q39" s="6" t="n">
         <v>2860</v>
       </c>
-      <c r="R39" s="11" t="n">
+      <c r="R39" s="12" t="n">
         <f aca="false">K39/I39*100</f>
-        <v>3.928035982009</v>
+        <v>3.92557235140439</v>
       </c>
       <c r="S39" s="5" t="n">
         <v>131.25</v>
@@ -32604,7 +32609,7 @@
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
-      <c r="W39" s="6" t="n">
+      <c r="W39" s="11" t="n">
         <v>2668.45426666667</v>
       </c>
       <c r="X39" s="5"/>
@@ -32635,17 +32640,17 @@
       <c r="H40" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I40" s="6" t="n">
-        <v>3457</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="L40" s="6" t="n">
-        <v>48.4</v>
+      <c r="I40" s="11" t="n">
+        <v>3456.97324</v>
+      </c>
+      <c r="J40" s="11" t="n">
+        <v>231.524918915478</v>
+      </c>
+      <c r="K40" s="11" t="n">
+        <v>153.139398744334</v>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>48.4269299540824</v>
       </c>
       <c r="M40" s="6" t="n">
         <v>3432</v>
@@ -32662,9 +32667,9 @@
       <c r="Q40" s="6" t="n">
         <v>3714</v>
       </c>
-      <c r="R40" s="11" t="n">
+      <c r="R40" s="12" t="n">
         <f aca="false">K40/I40*100</f>
-        <v>4.42869540063639</v>
+        <v>4.42986937163371</v>
       </c>
       <c r="S40" s="5" t="n">
         <v>162.11</v>
@@ -32672,7 +32677,7 @@
       <c r="T40" s="5"/>
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
-      <c r="W40" s="6" t="n">
+      <c r="W40" s="11" t="n">
         <v>3456.97324</v>
       </c>
       <c r="X40" s="5"/>
@@ -32703,17 +32708,17 @@
       <c r="H41" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>3788</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>181.7</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="L41" s="6" t="n">
-        <v>38</v>
+      <c r="I41" s="11" t="n">
+        <v>3788.13705</v>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>181.685029858885</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>120.17339802457</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>38.002165191962</v>
       </c>
       <c r="M41" s="6" t="n">
         <v>3760</v>
@@ -32730,9 +32735,9 @@
       <c r="Q41" s="6" t="n">
         <v>3961</v>
       </c>
-      <c r="R41" s="11" t="n">
+      <c r="R41" s="12" t="n">
         <f aca="false">K41/I41*100</f>
-        <v>3.17317845828934</v>
+        <v>3.17236141244071</v>
       </c>
       <c r="S41" s="5" t="n">
         <v>224.09</v>
@@ -32740,7 +32745,7 @@
       <c r="T41" s="5"/>
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
-      <c r="W41" s="6" t="n">
+      <c r="W41" s="11" t="n">
         <v>3788.13705</v>
       </c>
       <c r="X41" s="5"/>
@@ -32771,17 +32776,17 @@
       <c r="H42" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I42" s="6" t="n">
-        <v>2805</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>69.4</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>21.9</v>
+      <c r="I42" s="11" t="n">
+        <v>2805.21441</v>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>104.927305650856</v>
+      </c>
+      <c r="K42" s="11" t="n">
+        <v>69.4029159992968</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>21.9471290815119</v>
       </c>
       <c r="M42" s="6" t="n">
         <v>2795</v>
@@ -32798,9 +32803,9 @@
       <c r="Q42" s="6" t="n">
         <v>2900</v>
       </c>
-      <c r="R42" s="11" t="n">
+      <c r="R42" s="12" t="n">
         <f aca="false">K42/I42*100</f>
-        <v>2.47415329768271</v>
+        <v>2.4740681408127</v>
       </c>
       <c r="S42" s="5" t="n">
         <v>116.02</v>
@@ -32808,7 +32813,7 @@
       <c r="T42" s="5"/>
       <c r="U42" s="5"/>
       <c r="V42" s="5"/>
-      <c r="W42" s="6" t="n">
+      <c r="W42" s="11" t="n">
         <v>2805.21441</v>
       </c>
       <c r="X42" s="5"/>
@@ -32839,17 +32844,17 @@
       <c r="H43" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I43" s="6" t="n">
-        <v>2770</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>200.7</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>132.7</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>42</v>
+      <c r="I43" s="11" t="n">
+        <v>2769.59611</v>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>200.670203110883</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>132.730914643026</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>41.9732006189358</v>
       </c>
       <c r="M43" s="6" t="n">
         <v>2705</v>
@@ -32866,9 +32871,9 @@
       <c r="Q43" s="6" t="n">
         <v>3015</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="12" t="n">
         <f aca="false">K43/I43*100</f>
-        <v>4.79061371841155</v>
+        <v>4.79242854811153</v>
       </c>
       <c r="S43" s="5" t="n">
         <v>131.25</v>
@@ -32876,7 +32881,7 @@
       <c r="T43" s="5"/>
       <c r="U43" s="5"/>
       <c r="V43" s="5"/>
-      <c r="W43" s="6" t="n">
+      <c r="W43" s="11" t="n">
         <v>2769.59611</v>
       </c>
       <c r="X43" s="5"/>
@@ -32907,17 +32912,17 @@
       <c r="H44" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="6" t="n">
-        <v>5635</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="L44" s="6" t="n">
-        <v>24.5</v>
+      <c r="I44" s="11" t="n">
+        <v>5635.3556875</v>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>132.268046448635</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>69.1787458158199</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>24.4583801401734</v>
       </c>
       <c r="M44" s="6" t="n">
         <v>5646</v>
@@ -32934,9 +32939,9 @@
       <c r="Q44" s="6" t="n">
         <v>5732</v>
       </c>
-      <c r="R44" s="11" t="n">
+      <c r="R44" s="12" t="n">
         <f aca="false">K44/I44*100</f>
-        <v>1.22803904170364</v>
+        <v>1.22758437358742</v>
       </c>
       <c r="S44" s="5" t="n">
         <v>131.33</v>
@@ -32944,7 +32949,7 @@
       <c r="T44" s="5"/>
       <c r="U44" s="5"/>
       <c r="V44" s="5"/>
-      <c r="W44" s="6" t="n">
+      <c r="W44" s="11" t="n">
         <v>5635.3556875</v>
       </c>
       <c r="X44" s="5"/>
@@ -32975,17 +32980,17 @@
       <c r="H45" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="6" t="n">
-        <v>6261</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>414.4</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>274.1</v>
-      </c>
-      <c r="L45" s="6" t="n">
-        <v>86.7</v>
+      <c r="I45" s="11" t="n">
+        <v>6261.0135</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>414.40384314605</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>274.1024839745</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>86.6788161669223</v>
       </c>
       <c r="M45" s="6" t="n">
         <v>6311</v>
@@ -33002,9 +33007,9 @@
       <c r="Q45" s="6" t="n">
         <v>6625</v>
       </c>
-      <c r="R45" s="11" t="n">
+      <c r="R45" s="12" t="n">
         <f aca="false">K45/I45*100</f>
-        <v>4.37789490496726</v>
+        <v>4.37792513902901</v>
       </c>
       <c r="S45" s="5" t="n">
         <v>162.15</v>
@@ -33012,7 +33017,7 @@
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
       <c r="V45" s="5"/>
-      <c r="W45" s="6" t="n">
+      <c r="W45" s="11" t="n">
         <v>6261.0135</v>
       </c>
       <c r="X45" s="5"/>
@@ -33043,17 +33048,17 @@
       <c r="H46" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I46" s="6" t="n">
-        <v>6644</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="L46" s="6" t="n">
-        <v>65.4</v>
+      <c r="I46" s="11" t="n">
+        <v>6643.5038</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>312.555765017917</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>206.736286327749</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>65.3757539800413</v>
       </c>
       <c r="M46" s="6" t="n">
         <v>6715</v>
@@ -33070,9 +33075,9 @@
       <c r="Q46" s="6" t="n">
         <v>6957</v>
       </c>
-      <c r="R46" s="11" t="n">
+      <c r="R46" s="12" t="n">
         <f aca="false">K46/I46*100</f>
-        <v>3.1110776640578</v>
+        <v>3.11185622152799</v>
       </c>
       <c r="S46" s="5" t="n">
         <v>224.11</v>
@@ -33080,7 +33085,7 @@
       <c r="T46" s="5"/>
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
-      <c r="W46" s="6" t="n">
+      <c r="W46" s="11" t="n">
         <v>6643.5038</v>
       </c>
       <c r="X46" s="5"/>
@@ -33111,17 +33116,17 @@
       <c r="H47" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I47" s="6" t="n">
-        <v>5542</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>433.9</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>287</v>
-      </c>
-      <c r="L47" s="6" t="n">
-        <v>90.8</v>
+      <c r="I47" s="11" t="n">
+        <v>5542.1856</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>433.890466344281</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>286.991678684569</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>90.7547374158433</v>
       </c>
       <c r="M47" s="6" t="n">
         <v>5590</v>
@@ -33138,9 +33143,9 @@
       <c r="Q47" s="6" t="n">
         <v>5889</v>
       </c>
-      <c r="R47" s="11" t="n">
+      <c r="R47" s="12" t="n">
         <f aca="false">K47/I47*100</f>
-        <v>5.17863587152653</v>
+        <v>5.17831230128</v>
       </c>
       <c r="S47" s="5" t="n">
         <v>116.19</v>
@@ -33148,7 +33153,7 @@
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
-      <c r="W47" s="6" t="n">
+      <c r="W47" s="11" t="n">
         <v>5542.1856</v>
       </c>
       <c r="X47" s="5"/>
@@ -33179,17 +33184,17 @@
       <c r="H48" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="I48" s="6" t="n">
-        <v>5517</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>166.1</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>98.9</v>
-      </c>
-      <c r="L48" s="6" t="n">
-        <v>33</v>
+      <c r="I48" s="11" t="n">
+        <v>5517.22597777778</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>166.132884401757</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>98.8630147076346</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>32.9543382358782</v>
       </c>
       <c r="M48" s="6" t="n">
         <v>5554</v>
@@ -33206,9 +33211,9 @@
       <c r="Q48" s="6" t="n">
         <v>5690</v>
       </c>
-      <c r="R48" s="11" t="n">
+      <c r="R48" s="12" t="n">
         <f aca="false">K48/I48*100</f>
-        <v>1.7926409280406</v>
+        <v>1.79189714370653</v>
       </c>
       <c r="S48" s="5" t="n">
         <v>131.33</v>
@@ -33216,7 +33221,7 @@
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
-      <c r="W48" s="6" t="n">
+      <c r="W48" s="11" t="n">
         <v>5517.22597777778</v>
       </c>
       <c r="X48" s="5"/>
@@ -33247,17 +33252,17 @@
       <c r="H49" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I49" s="6" t="n">
-        <v>131.7</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>8.22</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="L49" s="6" t="n">
-        <v>1.98</v>
+      <c r="I49" s="11" t="n">
+        <v>131.7396</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>8.21619331952041</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>7.685432329228</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>1.98437009463361</v>
       </c>
       <c r="M49" s="6" t="n">
         <v>126.4</v>
@@ -33274,9 +33279,9 @@
       <c r="Q49" s="6" t="n">
         <v>145.3</v>
       </c>
-      <c r="R49" s="11" t="n">
+      <c r="R49" s="12" t="n">
         <f aca="false">K49/I49*100</f>
-        <v>5.83902809415338</v>
+        <v>5.83380572677312</v>
       </c>
       <c r="S49" s="5" t="n">
         <v>15.12</v>
@@ -33284,7 +33289,7 @@
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
-      <c r="W49" s="6" t="n">
+      <c r="W49" s="11" t="n">
         <v>131.7396</v>
       </c>
       <c r="X49" s="5"/>
@@ -33315,17 +33320,17 @@
       <c r="H50" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I50" s="6" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>0.43</v>
+      <c r="I50" s="11" t="n">
+        <v>148.558028571429</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>1.81464093933423</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>1.60863192683844</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>0.429924966546817</v>
       </c>
       <c r="M50" s="6" t="n">
         <v>148.4</v>
@@ -33342,9 +33347,9 @@
       <c r="Q50" s="6" t="n">
         <v>151.5</v>
       </c>
-      <c r="R50" s="11" t="n">
+      <c r="R50" s="12" t="n">
         <f aca="false">K50/I50*100</f>
-        <v>1.08344549125168</v>
+        <v>1.08283069067855</v>
       </c>
       <c r="S50" s="5" t="n">
         <v>15.12</v>
@@ -33352,7 +33357,7 @@
       <c r="T50" s="5"/>
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
-      <c r="W50" s="6" t="n">
+      <c r="W50" s="11" t="n">
         <v>148.558028571429</v>
       </c>
       <c r="X50" s="5"/>
@@ -33383,17 +33388,17 @@
       <c r="H51" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I51" s="6" t="n">
-        <v>1660.9</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>2.85</v>
+      <c r="I51" s="11" t="n">
+        <v>1660.90716333333</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>11.7799520347244</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>11.0189744427424</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>2.84508696726842</v>
       </c>
       <c r="M51" s="6" t="n">
         <v>1660.8</v>
@@ -33410,9 +33415,9 @@
       <c r="Q51" s="6" t="n">
         <v>1680.7</v>
       </c>
-      <c r="R51" s="11" t="n">
+      <c r="R51" s="12" t="n">
         <f aca="false">K51/I51*100</f>
-        <v>0.663495695105064</v>
+        <v>0.663431086697705</v>
       </c>
       <c r="S51" s="5" t="n">
         <v>1</v>
@@ -33420,7 +33425,7 @@
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
       <c r="V51" s="5"/>
-      <c r="W51" s="6" t="n">
+      <c r="W51" s="11" t="n">
         <v>1660.90716333333</v>
       </c>
       <c r="X51" s="5"/>
@@ -33451,17 +33456,17 @@
       <c r="H52" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I52" s="6" t="n">
-        <v>364.6</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="L52" s="6" t="n">
-        <v>1.51</v>
+      <c r="I52" s="11" t="n">
+        <v>364.633033333333</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>6.23605408930083</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>5.83320886460405</v>
+      </c>
+      <c r="L52" s="11" t="n">
+        <v>1.50612805250406</v>
       </c>
       <c r="M52" s="6" t="n">
         <v>363.4</v>
@@ -33478,9 +33483,9 @@
       <c r="Q52" s="6" t="n">
         <v>376</v>
       </c>
-      <c r="R52" s="11" t="n">
+      <c r="R52" s="12" t="n">
         <f aca="false">K52/I52*100</f>
-        <v>1.5990126165661</v>
+        <v>1.59974778238799</v>
       </c>
       <c r="S52" s="5" t="n">
         <v>15.02</v>
@@ -33488,7 +33493,7 @@
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
       <c r="V52" s="5"/>
-      <c r="W52" s="6" t="n">
+      <c r="W52" s="11" t="n">
         <v>364.633033333333</v>
       </c>
       <c r="X52" s="5"/>
@@ -33519,17 +33524,17 @@
       <c r="H53" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <v>570</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>1.11</v>
+      <c r="I53" s="11" t="n">
+        <v>569.984653333333</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>4.60817558656641</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>4.31049030304753</v>
+      </c>
+      <c r="L53" s="11" t="n">
+        <v>1.11296381051278</v>
       </c>
       <c r="M53" s="6" t="n">
         <v>569.2</v>
@@ -33546,9 +33551,9 @@
       <c r="Q53" s="6" t="n">
         <v>577.4</v>
       </c>
-      <c r="R53" s="11" t="n">
+      <c r="R53" s="12" t="n">
         <f aca="false">K53/I53*100</f>
-        <v>0.756140350877193</v>
+        <v>0.756246730124979</v>
       </c>
       <c r="S53" s="5" t="n">
         <v>15.02</v>
@@ -33556,7 +33561,7 @@
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
-      <c r="W53" s="6" t="n">
+      <c r="W53" s="11" t="n">
         <v>569.984653333333</v>
       </c>
       <c r="X53" s="5"/>
@@ -33587,17 +33592,17 @@
       <c r="H54" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I54" s="6" t="n">
-        <v>147.1</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0.55</v>
+      <c r="I54" s="11" t="n">
+        <v>147.134464285714</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>2.30387904479604</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>2.04232876416459</v>
+      </c>
+      <c r="L54" s="11" t="n">
+        <v>0.545835321904095</v>
       </c>
       <c r="M54" s="6" t="n">
         <v>147.1</v>
@@ -33614,9 +33619,9 @@
       <c r="Q54" s="6" t="n">
         <v>150.5</v>
       </c>
-      <c r="R54" s="11" t="n">
+      <c r="R54" s="12" t="n">
         <f aca="false">K54/I54*100</f>
-        <v>1.38681169272604</v>
+        <v>1.38806959612037</v>
       </c>
       <c r="S54" s="5" t="n">
         <v>15.51</v>
@@ -33624,7 +33629,7 @@
       <c r="T54" s="5"/>
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
-      <c r="W54" s="6" t="n">
+      <c r="W54" s="11" t="n">
         <v>147.134464285714</v>
       </c>
       <c r="X54" s="5"/>
@@ -33655,17 +33660,17 @@
       <c r="H55" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I55" s="6" t="n">
-        <v>218.9</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>0.75</v>
+      <c r="I55" s="11" t="n">
+        <v>218.938507692308</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>3.25622755138231</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>2.71909748061789</v>
+      </c>
+      <c r="L55" s="11" t="n">
+        <v>0.754141953027135</v>
       </c>
       <c r="M55" s="6" t="n">
         <v>218.3</v>
@@ -33682,9 +33687,9 @@
       <c r="Q55" s="6" t="n">
         <v>225.5</v>
       </c>
-      <c r="R55" s="11" t="n">
+      <c r="R55" s="12" t="n">
         <f aca="false">K55/I55*100</f>
-        <v>1.24257651895843</v>
+        <v>1.24194574507618</v>
       </c>
       <c r="S55" s="5" t="n">
         <v>15.52</v>
@@ -33692,7 +33697,7 @@
       <c r="T55" s="5"/>
       <c r="U55" s="5"/>
       <c r="V55" s="5"/>
-      <c r="W55" s="6" t="n">
+      <c r="W55" s="11" t="n">
         <v>218.938507692308</v>
       </c>
       <c r="X55" s="5"/>
@@ -33723,17 +33728,17 @@
       <c r="H56" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I56" s="6" t="n">
-        <v>149.83</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>11.685</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>10.931</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>2.822</v>
+      <c r="I56" s="11" t="n">
+        <v>149.82536</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>11.6854077971479</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>10.9305377042486</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>2.82225269957647</v>
       </c>
       <c r="M56" s="6" t="n">
         <v>148.43</v>
@@ -33750,9 +33755,9 @@
       <c r="Q56" s="6" t="n">
         <v>169.17</v>
       </c>
-      <c r="R56" s="11" t="n">
+      <c r="R56" s="12" t="n">
         <f aca="false">K56/I56*100</f>
-        <v>7.29560168190616</v>
+        <v>7.29551906583011</v>
       </c>
       <c r="S56" s="5" t="n">
         <v>25.17</v>
@@ -33760,7 +33765,7 @@
       <c r="T56" s="5"/>
       <c r="U56" s="5"/>
       <c r="V56" s="5"/>
-      <c r="W56" s="6" t="n">
+      <c r="W56" s="11" t="n">
         <v>149.82536</v>
       </c>
       <c r="X56" s="5"/>
@@ -33791,17 +33796,17 @@
       <c r="H57" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I57" s="6" t="n">
-        <v>86.79</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>3.591</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>0.927</v>
+      <c r="I57" s="11" t="n">
+        <v>86.7900466666667</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>3.83950331175975</v>
+      </c>
+      <c r="K57" s="11" t="n">
+        <v>3.59147378023218</v>
+      </c>
+      <c r="L57" s="11" t="n">
+        <v>0.927314542611989</v>
       </c>
       <c r="M57" s="6" t="n">
         <v>86.53</v>
@@ -33818,9 +33823,9 @@
       <c r="Q57" s="6" t="n">
         <v>93.31</v>
       </c>
-      <c r="R57" s="11" t="n">
+      <c r="R57" s="12" t="n">
         <f aca="false">K57/I57*100</f>
-        <v>4.13757345316281</v>
+        <v>4.13811712076375</v>
       </c>
       <c r="S57" s="5" t="n">
         <v>25.09</v>
@@ -33828,7 +33833,7 @@
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
       <c r="V57" s="5"/>
-      <c r="W57" s="6" t="n">
+      <c r="W57" s="11" t="n">
         <v>86.7900466666667</v>
       </c>
       <c r="X57" s="5"/>
@@ -33859,17 +33864,17 @@
       <c r="H58" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I58" s="6" t="n">
-        <v>827.12</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>106.357</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>99.486</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>25.687</v>
+      <c r="I58" s="11" t="n">
+        <v>827.117506666667</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>106.357068392591</v>
+      </c>
+      <c r="K58" s="11" t="n">
+        <v>99.4864677689991</v>
+      </c>
+      <c r="L58" s="11" t="n">
+        <v>25.6872955228223</v>
       </c>
       <c r="M58" s="6" t="n">
         <v>877.72</v>
@@ -33886,9 +33891,9 @@
       <c r="Q58" s="6" t="n">
         <v>926.5</v>
       </c>
-      <c r="R58" s="11" t="n">
+      <c r="R58" s="12" t="n">
         <f aca="false">K58/I58*100</f>
-        <v>12.0280007737692</v>
+        <v>12.028093586114</v>
       </c>
       <c r="S58" s="5" t="n">
         <v>11</v>
@@ -33896,7 +33901,7 @@
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
       <c r="V58" s="5"/>
-      <c r="W58" s="6" t="n">
+      <c r="W58" s="11" t="n">
         <v>827.117506666667</v>
       </c>
       <c r="X58" s="5"/>
@@ -33927,17 +33932,17 @@
       <c r="H59" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I59" s="6" t="n">
-        <v>238.43</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>13.754</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>12.193</v>
-      </c>
-      <c r="L59" s="6" t="n">
-        <v>3.259</v>
+      <c r="I59" s="11" t="n">
+        <v>238.4256</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>13.754243992858</v>
+      </c>
+      <c r="K59" s="11" t="n">
+        <v>12.1927790434149</v>
+      </c>
+      <c r="L59" s="11" t="n">
+        <v>3.25865726950686</v>
       </c>
       <c r="M59" s="6" t="n">
         <v>242.56</v>
@@ -33954,9 +33959,9 @@
       <c r="Q59" s="6" t="n">
         <v>244.84</v>
       </c>
-      <c r="R59" s="11" t="n">
+      <c r="R59" s="12" t="n">
         <f aca="false">K59/I59*100</f>
-        <v>5.11386989892212</v>
+        <v>5.11387159911307</v>
       </c>
       <c r="S59" s="5" t="n">
         <v>25.02</v>
@@ -33964,7 +33969,7 @@
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
       <c r="V59" s="5"/>
-      <c r="W59" s="6" t="n">
+      <c r="W59" s="11" t="n">
         <v>238.4256</v>
       </c>
       <c r="X59" s="5"/>
@@ -33995,17 +34000,17 @@
       <c r="H60" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I60" s="6" t="n">
-        <v>122.83</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>7.437</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>6.956</v>
-      </c>
-      <c r="L60" s="6" t="n">
-        <v>1.796</v>
+      <c r="I60" s="11" t="n">
+        <v>122.830826666667</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>7.43691887776387</v>
+      </c>
+      <c r="K60" s="11" t="n">
+        <v>6.95649853286907</v>
+      </c>
+      <c r="L60" s="11" t="n">
+        <v>1.79616019771455</v>
       </c>
       <c r="M60" s="6" t="n">
         <v>124.66</v>
@@ -34022,9 +34027,9 @@
       <c r="Q60" s="6" t="n">
         <v>133.27</v>
       </c>
-      <c r="R60" s="11" t="n">
+      <c r="R60" s="12" t="n">
         <f aca="false">K60/I60*100</f>
-        <v>5.66311161768298</v>
+        <v>5.66347937374657</v>
       </c>
       <c r="S60" s="5" t="n">
         <v>25.51</v>
@@ -34032,7 +34037,7 @@
       <c r="T60" s="5"/>
       <c r="U60" s="5"/>
       <c r="V60" s="5"/>
-      <c r="W60" s="6" t="n">
+      <c r="W60" s="11" t="n">
         <v>122.830826666667</v>
       </c>
       <c r="X60" s="5"/>
@@ -34063,17 +34068,17 @@
       <c r="H61" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I61" s="6" t="n">
-        <v>106.78</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>2.994</v>
-      </c>
-      <c r="K61" s="6" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="L61" s="6" t="n">
-        <v>0.709</v>
+      <c r="I61" s="11" t="n">
+        <v>106.781714285714</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>2.9944609240672</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>2.65451161257936</v>
+      </c>
+      <c r="L61" s="11" t="n">
+        <v>0.709448070248912</v>
       </c>
       <c r="M61" s="6" t="n">
         <v>106.96</v>
@@ -34090,9 +34095,9 @@
       <c r="Q61" s="6" t="n">
         <v>111.21</v>
       </c>
-      <c r="R61" s="11" t="n">
+      <c r="R61" s="12" t="n">
         <f aca="false">K61/I61*100</f>
-        <v>2.48642067802959</v>
+        <v>2.48592339085016</v>
       </c>
       <c r="S61" s="5" t="n">
         <v>25.51</v>
@@ -34100,7 +34105,7 @@
       <c r="T61" s="5"/>
       <c r="U61" s="5"/>
       <c r="V61" s="5"/>
-      <c r="W61" s="6" t="n">
+      <c r="W61" s="11" t="n">
         <v>106.781714285714</v>
       </c>
       <c r="X61" s="5"/>
@@ -34131,17 +34136,17 @@
       <c r="H62" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I62" s="6" t="n">
-        <v>101.34</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>1.516</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="L62" s="6" t="n">
-        <v>0.366</v>
+      <c r="I62" s="11" t="n">
+        <v>101.34328</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>1.51555448035098</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>1.41765060132198</v>
+      </c>
+      <c r="L62" s="11" t="n">
+        <v>0.366035811310731</v>
       </c>
       <c r="M62" s="6" t="n">
         <v>101.5</v>
@@ -34158,9 +34163,9 @@
       <c r="Q62" s="6" t="n">
         <v>103.5</v>
       </c>
-      <c r="R62" s="11" t="n">
+      <c r="R62" s="12" t="n">
         <f aca="false">K62/I62*100</f>
-        <v>1.39925004933886</v>
+        <v>1.39885999478405</v>
       </c>
       <c r="S62" s="5" t="n">
         <v>25.51</v>
@@ -34168,7 +34173,7 @@
       <c r="T62" s="5"/>
       <c r="U62" s="5"/>
       <c r="V62" s="5"/>
-      <c r="W62" s="6" t="n">
+      <c r="W62" s="11" t="n">
         <v>101.34328</v>
       </c>
       <c r="X62" s="5"/>
@@ -34199,17 +34204,17 @@
       <c r="H63" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I63" s="6" t="n">
-        <v>121.92</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>7.531</v>
-      </c>
-      <c r="K63" s="6" t="n">
-        <v>7.044</v>
-      </c>
-      <c r="L63" s="6" t="n">
-        <v>1.819</v>
+      <c r="I63" s="11" t="n">
+        <v>121.924506666667</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>7.53068906659598</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>7.04421122568704</v>
+      </c>
+      <c r="L63" s="11" t="n">
+        <v>1.81880751761688</v>
       </c>
       <c r="M63" s="6" t="n">
         <v>122.66</v>
@@ -34226,9 +34231,9 @@
       <c r="Q63" s="6" t="n">
         <v>133.18</v>
       </c>
-      <c r="R63" s="11" t="n">
+      <c r="R63" s="12" t="n">
         <f aca="false">K63/I63*100</f>
-        <v>5.77755905511811</v>
+        <v>5.7775187435824</v>
       </c>
       <c r="S63" s="5" t="n">
         <v>25.51</v>
@@ -34236,7 +34241,7 @@
       <c r="T63" s="5"/>
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
-      <c r="W63" s="6" t="n">
+      <c r="W63" s="11" t="n">
         <v>121.924506666667</v>
       </c>
       <c r="X63" s="5"/>
@@ -34267,17 +34272,17 @@
       <c r="H64" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I64" s="6" t="n">
-        <v>332.54</v>
-      </c>
-      <c r="J64" s="6" t="n">
-        <v>25.234</v>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>23.604</v>
-      </c>
-      <c r="L64" s="6" t="n">
-        <v>6.095</v>
+      <c r="I64" s="11" t="n">
+        <v>332.538686666667</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>25.2341988679909</v>
+      </c>
+      <c r="K64" s="11" t="n">
+        <v>23.6040852789411</v>
+      </c>
+      <c r="L64" s="11" t="n">
+        <v>6.0945486125199</v>
       </c>
       <c r="M64" s="6" t="n">
         <v>339.76</v>
@@ -34294,9 +34299,9 @@
       <c r="Q64" s="6" t="n">
         <v>363.7</v>
       </c>
-      <c r="R64" s="11" t="n">
+      <c r="R64" s="12" t="n">
         <f aca="false">K64/I64*100</f>
-        <v>7.09809346244061</v>
+        <v>7.09814714057664</v>
       </c>
       <c r="S64" s="5" t="n">
         <v>25.52</v>
@@ -34304,7 +34309,7 @@
       <c r="T64" s="5"/>
       <c r="U64" s="5"/>
       <c r="V64" s="5"/>
-      <c r="W64" s="6" t="n">
+      <c r="W64" s="11" t="n">
         <v>332.538686666667</v>
       </c>
       <c r="X64" s="5"/>
@@ -34335,17 +34340,17 @@
       <c r="H65" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I65" s="6" t="n">
-        <v>645.38</v>
-      </c>
-      <c r="J65" s="6" t="n">
-        <v>7.342</v>
-      </c>
-      <c r="K65" s="6" t="n">
-        <v>6.131</v>
-      </c>
-      <c r="L65" s="6" t="n">
-        <v>1.7</v>
+      <c r="I65" s="11" t="n">
+        <v>645.382607692308</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>7.34196440855411</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>6.13087280021661</v>
+      </c>
+      <c r="L65" s="11" t="n">
+        <v>1.70039817265604</v>
       </c>
       <c r="M65" s="6" t="n">
         <v>644.49</v>
@@ -34362,9 +34367,9 @@
       <c r="Q65" s="6" t="n">
         <v>660.26</v>
       </c>
-      <c r="R65" s="11" t="n">
+      <c r="R65" s="12" t="n">
         <f aca="false">K65/I65*100</f>
-        <v>0.949982955777991</v>
+        <v>0.949959408131364</v>
       </c>
       <c r="S65" s="5" t="n">
         <v>25.52</v>
@@ -34372,7 +34377,7 @@
       <c r="T65" s="5"/>
       <c r="U65" s="5"/>
       <c r="V65" s="5"/>
-      <c r="W65" s="6" t="n">
+      <c r="W65" s="11" t="n">
         <v>645.382607692308</v>
       </c>
       <c r="X65" s="5"/>
@@ -34403,17 +34408,17 @@
       <c r="H66" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I66" s="6" t="n">
-        <v>146.08</v>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>2.959</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>2.768</v>
-      </c>
-      <c r="L66" s="6" t="n">
-        <v>0.715</v>
+      <c r="I66" s="11" t="n">
+        <v>146.076266666667</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>2.95920830969418</v>
+      </c>
+      <c r="K66" s="11" t="n">
+        <v>2.76804528907692</v>
+      </c>
+      <c r="L66" s="11" t="n">
+        <v>0.714706220409522</v>
       </c>
       <c r="M66" s="6" t="n">
         <v>146.45</v>
@@ -34430,9 +34435,9 @@
       <c r="Q66" s="6" t="n">
         <v>150.22</v>
       </c>
-      <c r="R66" s="11" t="n">
+      <c r="R66" s="12" t="n">
         <f aca="false">K66/I66*100</f>
-        <v>1.89485213581599</v>
+        <v>1.89493156707884</v>
       </c>
       <c r="S66" s="5" t="n">
         <v>25.52</v>
@@ -34440,7 +34445,7 @@
       <c r="T66" s="5"/>
       <c r="U66" s="5"/>
       <c r="V66" s="5"/>
-      <c r="W66" s="6" t="n">
+      <c r="W66" s="11" t="n">
         <v>146.076266666667</v>
       </c>
       <c r="X66" s="5"/>
@@ -34471,17 +34476,17 @@
       <c r="H67" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I67" s="6" t="n">
-        <v>333.99</v>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>23.165</v>
-      </c>
-      <c r="K67" s="6" t="n">
-        <v>21.669</v>
-      </c>
-      <c r="L67" s="6" t="n">
-        <v>5.595</v>
+      <c r="I67" s="11" t="n">
+        <v>333.99058</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>23.1650986188209</v>
+      </c>
+      <c r="K67" s="11" t="n">
+        <v>21.6686476219906</v>
+      </c>
+      <c r="L67" s="11" t="n">
+        <v>5.59482075832044</v>
       </c>
       <c r="M67" s="6" t="n">
         <v>331.93</v>
@@ -34498,9 +34503,9 @@
       <c r="Q67" s="6" t="n">
         <v>372.04</v>
       </c>
-      <c r="R67" s="11" t="n">
+      <c r="R67" s="12" t="n">
         <f aca="false">K67/I67*100</f>
-        <v>6.48791879996407</v>
+        <v>6.48780202782684</v>
       </c>
       <c r="S67" s="5" t="n">
         <v>25.52</v>
@@ -34508,7 +34513,7 @@
       <c r="T67" s="5"/>
       <c r="U67" s="5"/>
       <c r="V67" s="5"/>
-      <c r="W67" s="6" t="n">
+      <c r="W67" s="11" t="n">
         <v>333.99058</v>
       </c>
       <c r="X67" s="5"/>
@@ -34539,17 +34544,17 @@
       <c r="H68" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I68" s="6" t="n">
-        <v>792.9</v>
-      </c>
-      <c r="J68" s="6" t="n">
-        <v>132.04</v>
-      </c>
-      <c r="K68" s="6" t="n">
-        <v>123.511</v>
-      </c>
-      <c r="L68" s="6" t="n">
-        <v>31.89</v>
+      <c r="I68" s="11" t="n">
+        <v>792.90042</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>132.040302118577</v>
+      </c>
+      <c r="K68" s="11" t="n">
+        <v>123.510580532735</v>
+      </c>
+      <c r="L68" s="11" t="n">
+        <v>31.8902947655794</v>
       </c>
       <c r="M68" s="6" t="n">
         <v>815.25</v>
@@ -34566,9 +34571,9 @@
       <c r="Q68" s="6" t="n">
         <v>1017.8</v>
       </c>
-      <c r="R68" s="11" t="n">
+      <c r="R68" s="12" t="n">
         <f aca="false">K68/I68*100</f>
-        <v>15.5771219573717</v>
+        <v>15.5770608032639</v>
       </c>
       <c r="S68" s="5" t="n">
         <v>11</v>
@@ -34576,7 +34581,7 @@
       <c r="T68" s="5"/>
       <c r="U68" s="5"/>
       <c r="V68" s="5"/>
-      <c r="W68" s="6" t="n">
+      <c r="W68" s="11" t="n">
         <v>792.90042</v>
       </c>
       <c r="X68" s="5"/>
@@ -34607,17 +34612,17 @@
       <c r="H69" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I69" s="6" t="n">
-        <v>237.97</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>6.767</v>
-      </c>
-      <c r="L69" s="6" t="n">
-        <v>1.747</v>
+      <c r="I69" s="11" t="n">
+        <v>237.965586666667</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>7.23392307385544</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>6.76661613193422</v>
+      </c>
+      <c r="L69" s="11" t="n">
+        <v>1.74713277261064</v>
       </c>
       <c r="M69" s="6" t="n">
         <v>240.31</v>
@@ -34634,9 +34639,9 @@
       <c r="Q69" s="6" t="n">
         <v>242.4</v>
       </c>
-      <c r="R69" s="11" t="n">
+      <c r="R69" s="12" t="n">
         <f aca="false">K69/I69*100</f>
-        <v>2.84363575240577</v>
+        <v>2.84352717832795</v>
       </c>
       <c r="S69" s="5" t="n">
         <v>25.02</v>
@@ -34644,7 +34649,7 @@
       <c r="T69" s="5"/>
       <c r="U69" s="5"/>
       <c r="V69" s="5"/>
-      <c r="W69" s="6" t="n">
+      <c r="W69" s="11" t="n">
         <v>237.965586666667</v>
       </c>
       <c r="X69" s="5"/>
@@ -34675,17 +34680,17 @@
       <c r="H70" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I70" s="6" t="n">
-        <v>107.06</v>
-      </c>
-      <c r="J70" s="6" t="n">
-        <v>8.123</v>
-      </c>
-      <c r="K70" s="6" t="n">
-        <v>7.201</v>
-      </c>
-      <c r="L70" s="6" t="n">
-        <v>1.924</v>
+      <c r="I70" s="11" t="n">
+        <v>107.059964285714</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>8.122840988867</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>7.20068696131002</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>1.92446453990232</v>
       </c>
       <c r="M70" s="6" t="n">
         <v>105.93</v>
@@ -34702,9 +34707,9 @@
       <c r="Q70" s="6" t="n">
         <v>116.8</v>
       </c>
-      <c r="R70" s="11" t="n">
+      <c r="R70" s="12" t="n">
         <f aca="false">K70/I70*100</f>
-        <v>6.72613487763871</v>
+        <v>6.72584472575885</v>
       </c>
       <c r="S70" s="5" t="n">
         <v>25.51</v>
@@ -34712,7 +34717,7 @@
       <c r="T70" s="5"/>
       <c r="U70" s="5"/>
       <c r="V70" s="5"/>
-      <c r="W70" s="6" t="n">
+      <c r="W70" s="11" t="n">
         <v>107.059964285714</v>
       </c>
       <c r="X70" s="5"/>
@@ -34743,17 +34748,17 @@
       <c r="H71" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I71" s="6" t="n">
-        <v>102.38</v>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="K71" s="6" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="L71" s="6" t="n">
-        <v>0.186</v>
+      <c r="I71" s="11" t="n">
+        <v>102.38169</v>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>0.770709445845419</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>0.720922093869077</v>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>0.186141284231194</v>
       </c>
       <c r="M71" s="6" t="n">
         <v>102.37</v>
@@ -34770,9 +34775,9 @@
       <c r="Q71" s="6" t="n">
         <v>104.2</v>
       </c>
-      <c r="R71" s="11" t="n">
+      <c r="R71" s="12" t="n">
         <f aca="false">K71/I71*100</f>
-        <v>0.704239109201016</v>
+        <v>0.704151390613963</v>
       </c>
       <c r="S71" s="5" t="n">
         <v>25.51</v>
@@ -34780,7 +34785,7 @@
       <c r="T71" s="5"/>
       <c r="U71" s="5"/>
       <c r="V71" s="5"/>
-      <c r="W71" s="6" t="n">
+      <c r="W71" s="11" t="n">
         <v>102.38169</v>
       </c>
       <c r="X71" s="5"/>
@@ -34811,17 +34816,17 @@
       <c r="H72" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I72" s="6" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>1.182</v>
-      </c>
-      <c r="L72" s="6" t="n">
-        <v>0.316</v>
+      <c r="I72" s="11" t="n">
+        <v>98.6988857142857</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>1.33309896562538</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>1.18175750985044</v>
+      </c>
+      <c r="L72" s="11" t="n">
+        <v>0.315837979721963</v>
       </c>
       <c r="M72" s="6" t="n">
         <v>98.78</v>
@@ -34838,9 +34843,9 @@
       <c r="Q72" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="R72" s="11" t="n">
+      <c r="R72" s="12" t="n">
         <f aca="false">K72/I72*100</f>
-        <v>1.19756838905775</v>
+        <v>1.19733622248928</v>
       </c>
       <c r="S72" s="5" t="n">
         <v>25.51</v>
@@ -34848,7 +34853,7 @@
       <c r="T72" s="5"/>
       <c r="U72" s="5"/>
       <c r="V72" s="5"/>
-      <c r="W72" s="6" t="n">
+      <c r="W72" s="11" t="n">
         <v>98.6988857142857</v>
       </c>
       <c r="X72" s="5"/>
@@ -34879,17 +34884,17 @@
       <c r="H73" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I73" s="6" t="n">
-        <v>250.33</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>33.074</v>
-      </c>
-      <c r="K73" s="6" t="n">
-        <v>30.938</v>
-      </c>
-      <c r="L73" s="6" t="n">
-        <v>7.988</v>
+      <c r="I73" s="11" t="n">
+        <v>250.326873333333</v>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>33.0742808775451</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>30.9377028554496</v>
+      </c>
+      <c r="L73" s="11" t="n">
+        <v>7.98808052860467</v>
       </c>
       <c r="M73" s="6" t="n">
         <v>245.63</v>
@@ -34906,9 +34911,9 @@
       <c r="Q73" s="6" t="n">
         <v>312.8</v>
       </c>
-      <c r="R73" s="11" t="n">
+      <c r="R73" s="12" t="n">
         <f aca="false">K73/I73*100</f>
-        <v>12.3588862701234</v>
+        <v>12.3589219341438</v>
       </c>
       <c r="S73" s="5" t="n">
         <v>25.52</v>
@@ -34916,7 +34921,7 @@
       <c r="T73" s="5"/>
       <c r="U73" s="5"/>
       <c r="V73" s="5"/>
-      <c r="W73" s="6" t="n">
+      <c r="W73" s="11" t="n">
         <v>250.326873333333</v>
       </c>
       <c r="X73" s="5"/>
@@ -34947,17 +34952,17 @@
       <c r="H74" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I74" s="6" t="n">
-        <v>644.7</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>3.542</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>3.313</v>
-      </c>
-      <c r="L74" s="6" t="n">
-        <v>0.855</v>
+      <c r="I74" s="11" t="n">
+        <v>644.695793333333</v>
+      </c>
+      <c r="J74" s="11" t="n">
+        <v>3.54206989864425</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>3.31325438104648</v>
+      </c>
+      <c r="L74" s="11" t="n">
+        <v>0.855478602636119</v>
       </c>
       <c r="M74" s="6" t="n">
         <v>645.84</v>
@@ -34974,9 +34979,9 @@
       <c r="Q74" s="6" t="n">
         <v>649</v>
       </c>
-      <c r="R74" s="11" t="n">
+      <c r="R74" s="12" t="n">
         <f aca="false">K74/I74*100</f>
-        <v>0.513882425934543</v>
+        <v>0.513925236570203</v>
       </c>
       <c r="S74" s="5" t="n">
         <v>25.52</v>
@@ -34984,7 +34989,7 @@
       <c r="T74" s="5"/>
       <c r="U74" s="5"/>
       <c r="V74" s="5"/>
-      <c r="W74" s="6" t="n">
+      <c r="W74" s="11" t="n">
         <v>644.695793333333</v>
       </c>
       <c r="X74" s="5"/>
@@ -35015,17 +35020,17 @@
       <c r="H75" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <v>146.34</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>2.148</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>1.904</v>
-      </c>
-      <c r="L75" s="6" t="n">
-        <v>0.509</v>
+      <c r="I75" s="11" t="n">
+        <v>146.339535714286</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>2.14768485024364</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>1.90386667907795</v>
+      </c>
+      <c r="L75" s="11" t="n">
+        <v>0.508829773086056</v>
       </c>
       <c r="M75" s="6" t="n">
         <v>146.67</v>
@@ -35042,9 +35047,9 @@
       <c r="Q75" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="R75" s="11" t="n">
+      <c r="R75" s="12" t="n">
         <f aca="false">K75/I75*100</f>
-        <v>1.30107967746344</v>
+        <v>1.30099270151784</v>
       </c>
       <c r="S75" s="5" t="n">
         <v>25.52</v>
@@ -35052,7 +35057,7 @@
       <c r="T75" s="5"/>
       <c r="U75" s="5"/>
       <c r="V75" s="5"/>
-      <c r="W75" s="6" t="n">
+      <c r="W75" s="11" t="n">
         <v>146.339535714286</v>
       </c>
       <c r="X75" s="5"/>
@@ -35083,17 +35088,17 @@
       <c r="H76" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>834.84</v>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>124.152</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>116.132</v>
-      </c>
-      <c r="L76" s="6" t="n">
-        <v>29.985</v>
+      <c r="I76" s="11" t="n">
+        <v>834.83908</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>124.152285610729</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>116.132124996779</v>
+      </c>
+      <c r="L76" s="11" t="n">
+        <v>29.9851857381468</v>
       </c>
       <c r="M76" s="6" t="n">
         <v>847.76</v>
@@ -35110,9 +35115,9 @@
       <c r="Q76" s="6" t="n">
         <v>1011.1</v>
       </c>
-      <c r="R76" s="11" t="n">
+      <c r="R76" s="12" t="n">
         <f aca="false">K76/I76*100</f>
-        <v>13.910689473432</v>
+        <v>13.9107197756936</v>
       </c>
       <c r="S76" s="5" t="n">
         <v>11</v>
@@ -35120,7 +35125,7 @@
       <c r="T76" s="5"/>
       <c r="U76" s="5"/>
       <c r="V76" s="5"/>
-      <c r="W76" s="6" t="n">
+      <c r="W76" s="11" t="n">
         <v>834.83908</v>
       </c>
       <c r="X76" s="5"/>
@@ -35151,17 +35156,17 @@
       <c r="H77" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <v>235.15</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>13.359</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>12.496</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>3.227</v>
+      <c r="I77" s="11" t="n">
+        <v>235.154093333333</v>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>13.3594952565137</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>12.4964801525108</v>
+      </c>
+      <c r="L77" s="11" t="n">
+        <v>3.22657730112571</v>
       </c>
       <c r="M77" s="6" t="n">
         <v>240.69</v>
@@ -35178,9 +35183,9 @@
       <c r="Q77" s="6" t="n">
         <v>246.2</v>
       </c>
-      <c r="R77" s="11" t="n">
+      <c r="R77" s="12" t="n">
         <f aca="false">K77/I77*100</f>
-        <v>5.31405485860089</v>
+        <v>5.31416654304072</v>
       </c>
       <c r="S77" s="5" t="n">
         <v>25.02</v>
@@ -35188,7 +35193,7 @@
       <c r="T77" s="5"/>
       <c r="U77" s="5"/>
       <c r="V77" s="5"/>
-      <c r="W77" s="6" t="n">
+      <c r="W77" s="11" t="n">
         <v>235.154093333333</v>
       </c>
       <c r="X77" s="5"/>
@@ -35219,17 +35224,17 @@
       <c r="H78" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I78" s="6" t="n">
-        <v>120.22</v>
-      </c>
-      <c r="J78" s="6" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="K78" s="6" t="n">
-        <v>5.362</v>
-      </c>
-      <c r="L78" s="6" t="n">
-        <v>1.385</v>
+      <c r="I78" s="11" t="n">
+        <v>120.216586666667</v>
+      </c>
+      <c r="J78" s="11" t="n">
+        <v>5.73280667597577</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>5.36247092191473</v>
+      </c>
+      <c r="L78" s="11" t="n">
+        <v>1.38458403833982</v>
       </c>
       <c r="M78" s="6" t="n">
         <v>119.52</v>
@@ -35246,9 +35251,9 @@
       <c r="Q78" s="6" t="n">
         <v>129.4</v>
       </c>
-      <c r="R78" s="11" t="n">
+      <c r="R78" s="12" t="n">
         <f aca="false">K78/I78*100</f>
-        <v>4.46015637997006</v>
+        <v>4.46067474597631</v>
       </c>
       <c r="S78" s="5" t="n">
         <v>25.51</v>
@@ -35256,7 +35261,7 @@
       <c r="T78" s="5"/>
       <c r="U78" s="5"/>
       <c r="V78" s="5"/>
-      <c r="W78" s="6" t="n">
+      <c r="W78" s="11" t="n">
         <v>120.216586666667</v>
       </c>
       <c r="X78" s="5"/>
@@ -35287,17 +35292,17 @@
       <c r="H79" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I79" s="6" t="n">
-        <v>105.12</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K79" s="6" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="L79" s="6" t="n">
-        <v>0.403</v>
+      <c r="I79" s="11" t="n">
+        <v>105.123746666667</v>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>1.66709756942016</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>1.55940410086979</v>
+      </c>
+      <c r="L79" s="11" t="n">
+        <v>0.402636407511751</v>
       </c>
       <c r="M79" s="6" t="n">
         <v>105.29</v>
@@ -35314,9 +35319,9 @@
       <c r="Q79" s="6" t="n">
         <v>107.8</v>
       </c>
-      <c r="R79" s="11" t="n">
+      <c r="R79" s="12" t="n">
         <f aca="false">K79/I79*100</f>
-        <v>1.48306697108067</v>
+        <v>1.48339851871381</v>
       </c>
       <c r="S79" s="5" t="n">
         <v>25.51</v>
@@ -35324,7 +35329,7 @@
       <c r="T79" s="5"/>
       <c r="U79" s="5"/>
       <c r="V79" s="5"/>
-      <c r="W79" s="6" t="n">
+      <c r="W79" s="11" t="n">
         <v>105.123746666667</v>
       </c>
       <c r="X79" s="5"/>
@@ -35355,17 +35360,17 @@
       <c r="H80" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I80" s="6" t="n">
-        <v>101.15</v>
-      </c>
-      <c r="J80" s="6" t="n">
-        <v>1.549</v>
-      </c>
-      <c r="K80" s="6" t="n">
-        <v>1.294</v>
-      </c>
-      <c r="L80" s="6" t="n">
-        <v>0.359</v>
+      <c r="I80" s="11" t="n">
+        <v>101.152053846154</v>
+      </c>
+      <c r="J80" s="11" t="n">
+        <v>1.54921967449746</v>
+      </c>
+      <c r="K80" s="11" t="n">
+        <v>1.29366859268218</v>
+      </c>
+      <c r="L80" s="11" t="n">
+        <v>0.358799111105612</v>
       </c>
       <c r="M80" s="6" t="n">
         <v>101.48</v>
@@ -35382,9 +35387,9 @@
       <c r="Q80" s="6" t="n">
         <v>103.6</v>
       </c>
-      <c r="R80" s="11" t="n">
+      <c r="R80" s="12" t="n">
         <f aca="false">K80/I80*100</f>
-        <v>1.27928818586258</v>
+        <v>1.27893457769011</v>
       </c>
       <c r="S80" s="5" t="n">
         <v>25.51</v>
@@ -35392,7 +35397,7 @@
       <c r="T80" s="5"/>
       <c r="U80" s="5"/>
       <c r="V80" s="5"/>
-      <c r="W80" s="6" t="n">
+      <c r="W80" s="11" t="n">
         <v>101.152053846154</v>
       </c>
       <c r="X80" s="5"/>
@@ -35423,17 +35428,17 @@
       <c r="H81" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>325.92</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>24.871</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>23.265</v>
-      </c>
-      <c r="L81" s="6" t="n">
-        <v>6.007</v>
+      <c r="I81" s="11" t="n">
+        <v>325.917833333333</v>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>24.871303400675</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>23.2646326336372</v>
+      </c>
+      <c r="L81" s="11" t="n">
+        <v>6.00690231638069</v>
       </c>
       <c r="M81" s="6" t="n">
         <v>322.04</v>
@@ -35450,9 +35455,9 @@
       <c r="Q81" s="6" t="n">
         <v>360.2</v>
       </c>
-      <c r="R81" s="11" t="n">
+      <c r="R81" s="12" t="n">
         <f aca="false">K81/I81*100</f>
-        <v>7.13825478645066</v>
+        <v>7.13818952332173</v>
       </c>
       <c r="S81" s="5" t="n">
         <v>25.52</v>
@@ -35460,7 +35465,7 @@
       <c r="T81" s="5"/>
       <c r="U81" s="5"/>
       <c r="V81" s="5"/>
-      <c r="W81" s="6" t="n">
+      <c r="W81" s="11" t="n">
         <v>325.917833333333</v>
       </c>
       <c r="X81" s="5"/>
@@ -35491,17 +35496,17 @@
       <c r="H82" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I82" s="6" t="n">
-        <v>642.72</v>
-      </c>
-      <c r="J82" s="6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K82" s="6" t="n">
-        <v>1.853</v>
-      </c>
-      <c r="L82" s="6" t="n">
-        <v>0.495</v>
+      <c r="I82" s="11" t="n">
+        <v>642.72345</v>
+      </c>
+      <c r="J82" s="11" t="n">
+        <v>2.09032140087916</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>1.85301547535985</v>
+      </c>
+      <c r="L82" s="11" t="n">
+        <v>0.495239217227615</v>
       </c>
       <c r="M82" s="6" t="n">
         <v>642.38</v>
@@ -35518,9 +35523,9 @@
       <c r="Q82" s="6" t="n">
         <v>646.6</v>
       </c>
-      <c r="R82" s="11" t="n">
+      <c r="R82" s="12" t="n">
         <f aca="false">K82/I82*100</f>
-        <v>0.288305949713717</v>
+        <v>0.288306809928881</v>
       </c>
       <c r="S82" s="5" t="n">
         <v>25.52</v>
@@ -35528,7 +35533,7 @@
       <c r="T82" s="5"/>
       <c r="U82" s="5"/>
       <c r="V82" s="5"/>
-      <c r="W82" s="6" t="n">
+      <c r="W82" s="11" t="n">
         <v>642.72345</v>
       </c>
       <c r="X82" s="5"/>
@@ -35559,17 +35564,17 @@
       <c r="H83" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I83" s="6" t="n">
-        <v>147.59</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>3.136</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>2.933</v>
-      </c>
-      <c r="L83" s="6" t="n">
-        <v>0.757</v>
+      <c r="I83" s="11" t="n">
+        <v>147.586866666667</v>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>3.13603919963502</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>2.93345301325117</v>
+      </c>
+      <c r="L83" s="11" t="n">
+        <v>0.757414311146917</v>
       </c>
       <c r="M83" s="6" t="n">
         <v>148.44</v>
@@ -35586,9 +35591,9 @@
       <c r="Q83" s="6" t="n">
         <v>150.8</v>
       </c>
-      <c r="R83" s="11" t="n">
+      <c r="R83" s="12" t="n">
         <f aca="false">K83/I83*100</f>
-        <v>1.98726200962125</v>
+        <v>1.9876111469163</v>
       </c>
       <c r="S83" s="5" t="n">
         <v>25.52</v>
@@ -35596,7 +35601,7 @@
       <c r="T83" s="5"/>
       <c r="U83" s="5"/>
       <c r="V83" s="5"/>
-      <c r="W83" s="6" t="n">
+      <c r="W83" s="11" t="n">
         <v>147.586866666667</v>
       </c>
       <c r="X83" s="5"/>
@@ -35627,17 +35632,17 @@
       <c r="H84" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I84" s="6" t="n">
-        <v>943.55</v>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>78.715</v>
-      </c>
-      <c r="K84" s="6" t="n">
-        <v>73.63</v>
-      </c>
-      <c r="L84" s="6" t="n">
-        <v>19.011</v>
+      <c r="I84" s="11" t="n">
+        <v>943.553853333333</v>
+      </c>
+      <c r="J84" s="11" t="n">
+        <v>78.7150293190011</v>
+      </c>
+      <c r="K84" s="11" t="n">
+        <v>73.6300872676756</v>
+      </c>
+      <c r="L84" s="11" t="n">
+        <v>19.0112067845004</v>
       </c>
       <c r="M84" s="6" t="n">
         <v>927.58</v>
@@ -35654,9 +35659,9 @@
       <c r="Q84" s="6" t="n">
         <v>1067.7</v>
       </c>
-      <c r="R84" s="11" t="n">
+      <c r="R84" s="12" t="n">
         <f aca="false">K84/I84*100</f>
-        <v>7.8035080281914</v>
+        <v>7.80348540865573</v>
       </c>
       <c r="S84" s="5" t="n">
         <v>11</v>
@@ -35664,7 +35669,7 @@
       <c r="T84" s="5"/>
       <c r="U84" s="5"/>
       <c r="V84" s="5"/>
-      <c r="W84" s="6" t="n">
+      <c r="W84" s="11" t="n">
         <v>943.553853333333</v>
       </c>
       <c r="X84" s="5"/>
@@ -35695,17 +35700,17 @@
       <c r="H85" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I85" s="6" t="n">
-        <v>241.69</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>6.664</v>
-      </c>
-      <c r="K85" s="6" t="n">
-        <v>5.565</v>
-      </c>
-      <c r="L85" s="6" t="n">
-        <v>1.543</v>
+      <c r="I85" s="11" t="n">
+        <v>241.691684615385</v>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>6.66431595243737</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>5.56500564852156</v>
+      </c>
+      <c r="L85" s="11" t="n">
+        <v>1.54345486261471</v>
       </c>
       <c r="M85" s="6" t="n">
         <v>243.16</v>
@@ -35722,9 +35727,9 @@
       <c r="Q85" s="6" t="n">
         <v>244.2</v>
       </c>
-      <c r="R85" s="11" t="n">
+      <c r="R85" s="12" t="n">
         <f aca="false">K85/I85*100</f>
-        <v>2.30253630683934</v>
+        <v>2.3025225950067</v>
       </c>
       <c r="S85" s="5" t="n">
         <v>25.02</v>
@@ -35732,7 +35737,7 @@
       <c r="T85" s="5"/>
       <c r="U85" s="5"/>
       <c r="V85" s="5"/>
-      <c r="W85" s="6" t="n">
+      <c r="W85" s="11" t="n">
         <v>241.691684615385</v>
       </c>
       <c r="X85" s="5"/>
@@ -35763,17 +35768,17 @@
       <c r="H86" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I86" s="6" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>6.336</v>
-      </c>
-      <c r="K86" s="6" t="n">
-        <v>5.927</v>
-      </c>
-      <c r="L86" s="6" t="n">
-        <v>1.53</v>
+      <c r="I86" s="11" t="n">
+        <v>124.495106666667</v>
+      </c>
+      <c r="J86" s="11" t="n">
+        <v>6.33616157564848</v>
+      </c>
+      <c r="K86" s="11" t="n">
+        <v>5.92684946945034</v>
+      </c>
+      <c r="L86" s="11" t="n">
+        <v>1.53030595271063</v>
       </c>
       <c r="M86" s="6" t="n">
         <v>124.26</v>
@@ -35790,9 +35795,9 @@
       <c r="Q86" s="6" t="n">
         <v>134.7</v>
       </c>
-      <c r="R86" s="11" t="n">
+      <c r="R86" s="12" t="n">
         <f aca="false">K86/I86*100</f>
-        <v>4.76064257028112</v>
+        <v>4.76070877654603</v>
       </c>
       <c r="S86" s="5" t="n">
         <v>25.51</v>
@@ -35800,7 +35805,7 @@
       <c r="T86" s="5"/>
       <c r="U86" s="5"/>
       <c r="V86" s="5"/>
-      <c r="W86" s="6" t="n">
+      <c r="W86" s="11" t="n">
         <v>124.495106666667</v>
       </c>
       <c r="X86" s="5"/>
@@ -35831,17 +35836,17 @@
       <c r="H87" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I87" s="6" t="n">
-        <v>104.51</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>2.053</v>
-      </c>
-      <c r="K87" s="6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="L87" s="6" t="n">
-        <v>0.496</v>
+      <c r="I87" s="11" t="n">
+        <v>104.513453333333</v>
+      </c>
+      <c r="J87" s="11" t="n">
+        <v>2.05288573412254</v>
+      </c>
+      <c r="K87" s="11" t="n">
+        <v>1.92027058951398</v>
+      </c>
+      <c r="L87" s="11" t="n">
+        <v>0.495811734226637</v>
       </c>
       <c r="M87" s="6" t="n">
         <v>104.86</v>
@@ -35858,9 +35863,9 @@
       <c r="Q87" s="6" t="n">
         <v>107.4</v>
       </c>
-      <c r="R87" s="11" t="n">
+      <c r="R87" s="12" t="n">
         <f aca="false">K87/I87*100</f>
-        <v>1.83714477083533</v>
+        <v>1.83734297190383</v>
       </c>
       <c r="S87" s="5" t="n">
         <v>25.51</v>
@@ -35868,7 +35873,7 @@
       <c r="T87" s="5"/>
       <c r="U87" s="5"/>
       <c r="V87" s="5"/>
-      <c r="W87" s="6" t="n">
+      <c r="W87" s="11" t="n">
         <v>104.513453333333</v>
       </c>
       <c r="X87" s="5"/>
@@ -35899,17 +35904,17 @@
       <c r="H88" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I88" s="6" t="n">
-        <v>99.44</v>
-      </c>
-      <c r="J88" s="6" t="n">
-        <v>2.177</v>
-      </c>
-      <c r="K88" s="6" t="n">
-        <v>2.036</v>
-      </c>
-      <c r="L88" s="6" t="n">
-        <v>0.526</v>
+      <c r="I88" s="11" t="n">
+        <v>99.43828</v>
+      </c>
+      <c r="J88" s="11" t="n">
+        <v>2.17669694454926</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>2.036083672572</v>
+      </c>
+      <c r="L88" s="11" t="n">
+        <v>0.525714543690413</v>
       </c>
       <c r="M88" s="6" t="n">
         <v>99.43</v>
@@ -35926,9 +35931,9 @@
       <c r="Q88" s="6" t="n">
         <v>102.4</v>
       </c>
-      <c r="R88" s="11" t="n">
+      <c r="R88" s="12" t="n">
         <f aca="false">K88/I88*100</f>
-        <v>2.04746580852776</v>
+        <v>2.04758536910735</v>
       </c>
       <c r="S88" s="5" t="n">
         <v>25.51</v>
@@ -35936,7 +35941,7 @@
       <c r="T88" s="5"/>
       <c r="U88" s="5"/>
       <c r="V88" s="5"/>
-      <c r="W88" s="6" t="n">
+      <c r="W88" s="11" t="n">
         <v>99.43828</v>
       </c>
       <c r="X88" s="5"/>
@@ -35967,17 +35972,17 @@
       <c r="H89" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I89" s="6" t="n">
-        <v>310.54</v>
-      </c>
-      <c r="J89" s="6" t="n">
-        <v>17.436</v>
-      </c>
-      <c r="K89" s="6" t="n">
-        <v>16.309</v>
-      </c>
-      <c r="L89" s="6" t="n">
-        <v>4.211</v>
+      <c r="I89" s="11" t="n">
+        <v>310.54116</v>
+      </c>
+      <c r="J89" s="11" t="n">
+        <v>17.4356644655376</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>16.3093313598951</v>
+      </c>
+      <c r="L89" s="11" t="n">
+        <v>4.21105124964347</v>
       </c>
       <c r="M89" s="6" t="n">
         <v>308.86</v>
@@ -35994,9 +35999,9 @@
       <c r="Q89" s="6" t="n">
         <v>342.2</v>
       </c>
-      <c r="R89" s="11" t="n">
+      <c r="R89" s="12" t="n">
         <f aca="false">K89/I89*100</f>
-        <v>5.25181941134798</v>
+        <v>5.25190649764272</v>
       </c>
       <c r="S89" s="5" t="n">
         <v>25.52</v>
@@ -36004,7 +36009,7 @@
       <c r="T89" s="5"/>
       <c r="U89" s="5"/>
       <c r="V89" s="5"/>
-      <c r="W89" s="6" t="n">
+      <c r="W89" s="11" t="n">
         <v>310.54116</v>
       </c>
       <c r="X89" s="5"/>
@@ -36035,17 +36040,17 @@
       <c r="H90" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I90" s="6" t="n">
-        <v>644.41</v>
-      </c>
-      <c r="J90" s="6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K90" s="6" t="n">
-        <v>3.414</v>
-      </c>
-      <c r="L90" s="6" t="n">
-        <v>0.881</v>
+      <c r="I90" s="11" t="n">
+        <v>644.414213333333</v>
+      </c>
+      <c r="J90" s="11" t="n">
+        <v>3.64960952703283</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>3.4138470161695</v>
+      </c>
+      <c r="L90" s="11" t="n">
+        <v>0.881451509341625</v>
       </c>
       <c r="M90" s="6" t="n">
         <v>644.36</v>
@@ -36062,9 +36067,9 @@
       <c r="Q90" s="6" t="n">
         <v>649.1</v>
       </c>
-      <c r="R90" s="11" t="n">
+      <c r="R90" s="12" t="n">
         <f aca="false">K90/I90*100</f>
-        <v>0.529786936888006</v>
+        <v>0.529759733031158</v>
       </c>
       <c r="S90" s="5" t="n">
         <v>25.52</v>
@@ -36072,7 +36077,7 @@
       <c r="T90" s="5"/>
       <c r="U90" s="5"/>
       <c r="V90" s="5"/>
-      <c r="W90" s="6" t="n">
+      <c r="W90" s="11" t="n">
         <v>644.414213333333</v>
       </c>
       <c r="X90" s="5"/>
@@ -36103,17 +36108,17 @@
       <c r="H91" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I91" s="6" t="n">
-        <v>147.53</v>
-      </c>
-      <c r="J91" s="6" t="n">
-        <v>3.036</v>
-      </c>
-      <c r="K91" s="6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L91" s="6" t="n">
-        <v>0.733</v>
+      <c r="I91" s="11" t="n">
+        <v>147.528046666667</v>
+      </c>
+      <c r="J91" s="11" t="n">
+        <v>3.03625228608121</v>
+      </c>
+      <c r="K91" s="11" t="n">
+        <v>2.84011227239515</v>
+      </c>
+      <c r="L91" s="11" t="n">
+        <v>0.733313835489714</v>
       </c>
       <c r="M91" s="6" t="n">
         <v>147.44</v>
@@ -36130,9 +36135,9 @@
       <c r="Q91" s="6" t="n">
         <v>151.4</v>
       </c>
-      <c r="R91" s="11" t="n">
+      <c r="R91" s="12" t="n">
         <f aca="false">K91/I91*100</f>
-        <v>1.92503219684132</v>
+        <v>1.92513378748399</v>
       </c>
       <c r="S91" s="5" t="n">
         <v>25.52</v>
@@ -36140,7 +36145,7 @@
       <c r="T91" s="5"/>
       <c r="U91" s="5"/>
       <c r="V91" s="5"/>
-      <c r="W91" s="6" t="n">
+      <c r="W91" s="11" t="n">
         <v>147.528046666667</v>
       </c>
       <c r="X91" s="5"/>
@@ -36171,17 +36176,17 @@
       <c r="H92" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I92" s="6" t="n">
-        <v>308.94</v>
-      </c>
-      <c r="J92" s="6" t="n">
-        <v>1.666</v>
-      </c>
-      <c r="K92" s="6" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="L92" s="6" t="n">
-        <v>0.402</v>
+      <c r="I92" s="11" t="n">
+        <v>308.94111</v>
+      </c>
+      <c r="J92" s="11" t="n">
+        <v>1.66620653248526</v>
+      </c>
+      <c r="K92" s="11" t="n">
+        <v>1.558570624368</v>
+      </c>
+      <c r="L92" s="11" t="n">
+        <v>0.402421204804358</v>
       </c>
       <c r="M92" s="6" t="n">
         <v>309.17</v>
@@ -36198,9 +36203,9 @@
       <c r="Q92" s="6" t="n">
         <v>311.4</v>
       </c>
-      <c r="R92" s="11" t="n">
+      <c r="R92" s="12" t="n">
         <f aca="false">K92/I92*100</f>
-        <v>0.504628730497831</v>
+        <v>0.504487934405363</v>
       </c>
       <c r="S92" s="5" t="n">
         <v>11</v>
@@ -36208,7 +36213,7 @@
       <c r="T92" s="5"/>
       <c r="U92" s="5"/>
       <c r="V92" s="5"/>
-      <c r="W92" s="6" t="n">
+      <c r="W92" s="11" t="n">
         <v>308.94111</v>
       </c>
       <c r="X92" s="5"/>
@@ -36239,17 +36244,17 @@
       <c r="H93" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I93" s="6" t="n">
-        <v>247.11</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>11.961</v>
-      </c>
-      <c r="K93" s="6" t="n">
-        <v>11.189</v>
-      </c>
-      <c r="L93" s="6" t="n">
-        <v>2.889</v>
+      <c r="I93" s="11" t="n">
+        <v>247.10553</v>
+      </c>
+      <c r="J93" s="11" t="n">
+        <v>11.9613130511428</v>
+      </c>
+      <c r="K93" s="11" t="n">
+        <v>11.1886196500347</v>
+      </c>
+      <c r="L93" s="11" t="n">
+        <v>2.88888917144223</v>
       </c>
       <c r="M93" s="6" t="n">
         <v>254.12</v>
@@ -36266,9 +36271,9 @@
       <c r="Q93" s="6" t="n">
         <v>256</v>
       </c>
-      <c r="R93" s="11" t="n">
+      <c r="R93" s="12" t="n">
         <f aca="false">K93/I93*100</f>
-        <v>4.52794302132654</v>
+        <v>4.52787100719062</v>
       </c>
       <c r="S93" s="5" t="n">
         <v>25.02</v>
@@ -36276,7 +36281,7 @@
       <c r="T93" s="5"/>
       <c r="U93" s="5"/>
       <c r="V93" s="5"/>
-      <c r="W93" s="6" t="n">
+      <c r="W93" s="11" t="n">
         <v>247.10553</v>
       </c>
       <c r="X93" s="5"/>
@@ -36307,17 +36312,17 @@
       <c r="H94" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I94" s="6" t="n">
-        <v>100.41</v>
-      </c>
-      <c r="J94" s="6" t="n">
-        <v>2.242</v>
-      </c>
-      <c r="K94" s="6" t="n">
-        <v>2.097</v>
-      </c>
-      <c r="L94" s="6" t="n">
-        <v>0.541</v>
+      <c r="I94" s="11" t="n">
+        <v>100.405693333333</v>
+      </c>
+      <c r="J94" s="11" t="n">
+        <v>2.24188601791747</v>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>2.09706157225045</v>
+      </c>
+      <c r="L94" s="11" t="n">
+        <v>0.541458969686502</v>
       </c>
       <c r="M94" s="6" t="n">
         <v>100.44</v>
@@ -36334,9 +36339,9 @@
       <c r="Q94" s="6" t="n">
         <v>104.4</v>
       </c>
-      <c r="R94" s="11" t="n">
+      <c r="R94" s="12" t="n">
         <f aca="false">K94/I94*100</f>
-        <v>2.08843740663281</v>
+        <v>2.08858830872119</v>
       </c>
       <c r="S94" s="5" t="n">
         <v>25.51</v>
@@ -36344,7 +36349,7 @@
       <c r="T94" s="5"/>
       <c r="U94" s="5"/>
       <c r="V94" s="5"/>
-      <c r="W94" s="6" t="n">
+      <c r="W94" s="11" t="n">
         <v>100.405693333333</v>
       </c>
       <c r="X94" s="5"/>
@@ -36375,17 +36380,17 @@
       <c r="H95" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I95" s="6" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="J95" s="6" t="n">
-        <v>1.574</v>
-      </c>
-      <c r="K95" s="6" t="n">
-        <v>1.472</v>
-      </c>
-      <c r="L95" s="6" t="n">
-        <v>0.38</v>
+      <c r="I95" s="11" t="n">
+        <v>103.49806</v>
+      </c>
+      <c r="J95" s="11" t="n">
+        <v>1.57400365099408</v>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>1.47232399180925</v>
+      </c>
+      <c r="L95" s="11" t="n">
+        <v>0.380152420033258</v>
       </c>
       <c r="M95" s="6" t="n">
         <v>103.07</v>
@@ -36402,9 +36407,9 @@
       <c r="Q95" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="R95" s="11" t="n">
+      <c r="R95" s="12" t="n">
         <f aca="false">K95/I95*100</f>
-        <v>1.42222222222222</v>
+        <v>1.42256192223241</v>
       </c>
       <c r="S95" s="5" t="n">
         <v>25.51</v>
@@ -36412,7 +36417,7 @@
       <c r="T95" s="5"/>
       <c r="U95" s="5"/>
       <c r="V95" s="5"/>
-      <c r="W95" s="6" t="n">
+      <c r="W95" s="11" t="n">
         <v>103.49806</v>
       </c>
       <c r="X95" s="5"/>
@@ -36443,17 +36448,17 @@
       <c r="H96" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I96" s="6" t="n">
-        <v>98.89</v>
-      </c>
-      <c r="J96" s="6" t="n">
-        <v>2.096</v>
-      </c>
-      <c r="K96" s="6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L96" s="6" t="n">
-        <v>0.485</v>
+      <c r="I96" s="11" t="n">
+        <v>98.8889538461538</v>
+      </c>
+      <c r="J96" s="11" t="n">
+        <v>2.09597488268991</v>
+      </c>
+      <c r="K96" s="11" t="n">
+        <v>1.75023395417841</v>
+      </c>
+      <c r="L96" s="11" t="n">
+        <v>0.48542755891141</v>
       </c>
       <c r="M96" s="6" t="n">
         <v>98.52</v>
@@ -36470,9 +36475,9 @@
       <c r="Q96" s="6" t="n">
         <v>102.9</v>
       </c>
-      <c r="R96" s="11" t="n">
+      <c r="R96" s="12" t="n">
         <f aca="false">K96/I96*100</f>
-        <v>1.76964303771868</v>
+        <v>1.76989834163007</v>
       </c>
       <c r="S96" s="5" t="n">
         <v>25.51</v>
@@ -36480,7 +36485,7 @@
       <c r="T96" s="5"/>
       <c r="U96" s="5"/>
       <c r="V96" s="5"/>
-      <c r="W96" s="6" t="n">
+      <c r="W96" s="11" t="n">
         <v>98.8889538461538</v>
       </c>
       <c r="X96" s="5"/>
@@ -36511,17 +36516,17 @@
       <c r="H97" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I97" s="6" t="n">
-        <v>150.05</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>2.215</v>
-      </c>
-      <c r="K97" s="6" t="n">
-        <v>2.072</v>
-      </c>
-      <c r="L97" s="6" t="n">
-        <v>0.535</v>
+      <c r="I97" s="11" t="n">
+        <v>150.050533333333</v>
+      </c>
+      <c r="J97" s="11" t="n">
+        <v>2.21461263218623</v>
+      </c>
+      <c r="K97" s="11" t="n">
+        <v>2.07155003031432</v>
+      </c>
+      <c r="L97" s="11" t="n">
+        <v>0.534871917882854</v>
       </c>
       <c r="M97" s="6" t="n">
         <v>149.66</v>
@@ -36538,9 +36543,9 @@
       <c r="Q97" s="6" t="n">
         <v>153.9</v>
       </c>
-      <c r="R97" s="11" t="n">
+      <c r="R97" s="12" t="n">
         <f aca="false">K97/I97*100</f>
-        <v>1.38087304231923</v>
+        <v>1.38056825543727</v>
       </c>
       <c r="S97" s="5" t="n">
         <v>25.52</v>
@@ -36548,7 +36553,7 @@
       <c r="T97" s="5"/>
       <c r="U97" s="5"/>
       <c r="V97" s="5"/>
-      <c r="W97" s="6" t="n">
+      <c r="W97" s="11" t="n">
         <v>150.050533333333</v>
       </c>
       <c r="X97" s="5"/>
@@ -36579,17 +36584,17 @@
       <c r="H98" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="I98" s="6" t="n">
-        <v>645.52</v>
-      </c>
-      <c r="J98" s="6" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="K98" s="6" t="n">
-        <v>2.765</v>
-      </c>
-      <c r="L98" s="6" t="n">
-        <v>0.739</v>
+      <c r="I98" s="11" t="n">
+        <v>645.522935714286</v>
+      </c>
+      <c r="J98" s="11" t="n">
+        <v>3.11869796724778</v>
+      </c>
+      <c r="K98" s="11" t="n">
+        <v>2.76464451536155</v>
+      </c>
+      <c r="L98" s="11" t="n">
+        <v>0.738882326621901</v>
       </c>
       <c r="M98" s="6" t="n">
         <v>645.17</v>
@@ -36606,9 +36611,9 @@
       <c r="Q98" s="6" t="n">
         <v>652.3</v>
       </c>
-      <c r="R98" s="11" t="n">
+      <c r="R98" s="12" t="n">
         <f aca="false">K98/I98*100</f>
-        <v>0.428336844714339</v>
+        <v>0.428279827470795</v>
       </c>
       <c r="S98" s="5" t="n">
         <v>25.52</v>
@@ -36616,7 +36621,7 @@
       <c r="T98" s="5"/>
       <c r="U98" s="5"/>
       <c r="V98" s="5"/>
-      <c r="W98" s="6" t="n">
+      <c r="W98" s="11" t="n">
         <v>645.522935714286</v>
       </c>
       <c r="X98" s="5"/>
@@ -36647,17 +36652,17 @@
       <c r="H99" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="I99" s="6" t="n">
-        <v>143.5</v>
-      </c>
-      <c r="J99" s="6" t="n">
-        <v>2.993</v>
-      </c>
-      <c r="K99" s="6" t="n">
-        <v>2.799</v>
-      </c>
-      <c r="L99" s="6" t="n">
-        <v>0.723</v>
+      <c r="I99" s="11" t="n">
+        <v>143.499486666667</v>
+      </c>
+      <c r="J99" s="11" t="n">
+        <v>2.99279924006382</v>
+      </c>
+      <c r="K99" s="11" t="n">
+        <v>2.79946626618786</v>
+      </c>
+      <c r="L99" s="11" t="n">
+        <v>0.722819081814337</v>
       </c>
       <c r="M99" s="6" t="n">
         <v>144.4</v>
@@ -36674,9 +36679,9 @@
       <c r="Q99" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="R99" s="11" t="n">
+      <c r="R99" s="12" t="n">
         <f aca="false">K99/I99*100</f>
-        <v>1.95052264808362</v>
+        <v>1.95085455092304</v>
       </c>
       <c r="S99" s="5" t="n">
         <v>25.52</v>
@@ -36684,7 +36689,7 @@
       <c r="T99" s="5"/>
       <c r="U99" s="5"/>
       <c r="V99" s="5"/>
-      <c r="W99" s="6" t="n">
+      <c r="W99" s="11" t="n">
         <v>143.499486666667</v>
       </c>
       <c r="X99" s="5"/>

--- a/results/Supplementary_Tables_S1-S6.xlsx
+++ b/results/Supplementary_Tables_S1-S6.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">S4_NIST — NIST SP 800-22 results (100 bitstreams of 10^6 bits per sequence): for every test (and every template, excursion state, or variant), the number of passing bitstreams and the P-value of the uniformity test. Sequences: three of the GPU filler function (three seeds) and one of the system generator of each of configurations B (OpenSSL) and C (Windows, BCryptGenRandom).</t>
   </si>
   <si>
-    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the revision kit (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean (Student t, N - 1 degrees of freedom); N = measured iterations after the removal of upper outliers, pooled over the processes. Mean, CI, SD and SE are computed from the times of these iterations in the BenchmarkDotNet logs, as BenchmarkDotNet computes them; they agree with its reports, which round them to three or four significant digits, and the manuscript uses them. Median, quartiles, extremes, allocation and collections are those of the reports. Process 1-3 = mean of the measured iterations of each process after the removal of upper outliers (WorkloadResult lines of the log).</t>
+    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the revision kit (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean (Student t, N - 1 degrees of freedom); N = measured iterations after the removal of upper outliers, pooled over the processes. Mean, CI, SD and SE are computed from the times of these iterations in the BenchmarkDotNet logs, as BenchmarkDotNet computes them; they agree with its reports, which give them rounded, and the manuscript uses them. Median, quartiles, extremes, allocation and collections are those of the reports. Process 1-3 = mean of the measured iterations of each process after the removal of upper outliers (WorkloadResult lines of the log).</t>
   </si>
   <si>
     <t xml:space="preserve">   Source: results/configuration_D of the repository (CSV reports and logs); analysis/config_d.py recomputes the tables of the manuscript and checks the means and N of the logs against the reports.</t>

--- a/results/Supplementary_Tables_S1-S6.xlsx
+++ b/results/Supplementary_Tables_S1-S6.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">S4_NIST — NIST SP 800-22 results (100 bitstreams of 10^6 bits per sequence): for every test (and every template, excursion state, or variant), the number of passing bitstreams and the P-value of the uniformity test. Sequences: three of the GPU filler function (three seeds) and one of the system generator of each of configurations B (OpenSSL) and C (Windows, BCryptGenRandom).</t>
   </si>
   <si>
-    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the revision kit (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean (Student t, N - 1 degrees of freedom); N = measured iterations after the removal of upper outliers, pooled over the processes. Mean, CI, SD and SE are computed from the times of these iterations in the BenchmarkDotNet logs, as BenchmarkDotNet computes them; they agree with its reports, which give them rounded, and the manuscript uses them. Median, quartiles, extremes, allocation and collections are those of the reports. Process 1-3 = mean of the measured iterations of each process after the removal of upper outliers (WorkloadResult lines of the log).</t>
+    <t xml:space="preserve">S5_ConfigD — BenchmarkDotNet statistics of configuration D (laptop ASUS ROG Strix SCAR 18; Intel Core i9-14900HX, 32 threads; Intel UHD Graphics via OpenCL; NVIDIA GeForce RTX 4090 Laptop GPU via CUDA; Windows 11 Home 25H2; .NET 8.0.33; BenchmarkDotNet 0.15.8; ILGPU 1.5.3), every case of the six benchmark classes of the measurement kit of configuration D (measurement/laptop): break-even grid (3 processes x (5 warm-up + 30 measured iterations)), 10 MB formation, recovery, and recognition (1 x (3 + 15)), 100 MB full cycle and chunk size (1 x (2 + 10)). Times in milliseconds; CI = half-width of the 99.9% confidence interval of the mean (Student t, N - 1 degrees of freedom); N = measured iterations after the removal of upper outliers, pooled over the processes. Mean, CI, SD and SE are computed from the times of these iterations in the BenchmarkDotNet logs, as BenchmarkDotNet computes them; they agree with its reports, which give them rounded, and the manuscript uses them. Median, quartiles, extremes, allocation and collections are those of the reports. Process 1-3 = mean of the measured iterations of each process after the removal of upper outliers (WorkloadResult lines of the log).</t>
   </si>
   <si>
     <t xml:space="preserve">   Source: results/configuration_D of the repository (CSV reports and logs); analysis/config_d.py recomputes the tables of the manuscript and checks the means and N of the logs against the reports.</t>
@@ -694,7 +694,7 @@
     <t xml:space="preserve">LinearComplexity</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S5. BenchmarkDotNet statistics of configuration D (all cases of the revision kit). Times in ms. Mean, CI, SD and SE computed from the iteration times of the BenchmarkDotNet logs (see README); CV = SD / Mean (formula). Process means from the logs; Process 2 and 3 empty for the classes run in one process.</t>
+    <t xml:space="preserve">Table S5. BenchmarkDotNet statistics of configuration D (all cases of the measurement kit of configuration D). Times in ms. Mean, CI, SD and SE computed from the iteration times of the BenchmarkDotNet logs (see README); CV = SD / Mean (formula). Process means from the logs; Process 2 and 3 empty for the classes run in one process.</t>
   </si>
   <si>
     <t xml:space="preserve">Class</t>
